--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X337"/>
+  <dimension ref="A1:X338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26661,6 +26661,84 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>335.89</v>
+      </c>
+      <c r="C338" t="n">
+        <v>319.95</v>
+      </c>
+      <c r="D338" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="E338" t="n">
+        <v>314.64</v>
+      </c>
+      <c r="F338" t="n">
+        <v>306.87</v>
+      </c>
+      <c r="G338" t="n">
+        <v>305.88</v>
+      </c>
+      <c r="H338" t="n">
+        <v>300.54</v>
+      </c>
+      <c r="I338" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="J338" t="n">
+        <v>307</v>
+      </c>
+      <c r="K338" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="L338" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="M338" t="n">
+        <v>310.31</v>
+      </c>
+      <c r="N338" t="n">
+        <v>341.15</v>
+      </c>
+      <c r="O338" t="n">
+        <v>335.32</v>
+      </c>
+      <c r="P338" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="R338" t="n">
+        <v>341.31</v>
+      </c>
+      <c r="S338" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="T338" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="U338" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="V338" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="W338" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26672,7 +26750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30225,6 +30303,16 @@
       </c>
       <c r="B355" t="n">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -30393,28 +30481,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4489791164188181</v>
+        <v>-0.4447749426331249</v>
       </c>
       <c r="J2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1086608972935229</v>
+        <v>0.1072515381296236</v>
       </c>
       <c r="M2" t="n">
-        <v>7.176534335154442</v>
+        <v>7.177426241169683</v>
       </c>
       <c r="N2" t="n">
-        <v>87.81799732771103</v>
+        <v>87.71219827086303</v>
       </c>
       <c r="O2" t="n">
-        <v>9.371125723610319</v>
+        <v>9.365479073216864</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4530609527995</v>
+        <v>340.4071928054701</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30471,28 +30559,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3784322888606889</v>
+        <v>-0.3785573796844496</v>
       </c>
       <c r="J3" t="n">
+        <v>337</v>
+      </c>
+      <c r="K3" t="n">
         <v>336</v>
       </c>
-      <c r="K3" t="n">
-        <v>335</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03565098281892987</v>
+        <v>0.03588019474058946</v>
       </c>
       <c r="M3" t="n">
-        <v>10.47297473608497</v>
+        <v>10.44234175052395</v>
       </c>
       <c r="N3" t="n">
-        <v>205.9899513133934</v>
+        <v>205.3770249821788</v>
       </c>
       <c r="O3" t="n">
-        <v>14.35235002755275</v>
+        <v>14.33098129864731</v>
       </c>
       <c r="P3" t="n">
-        <v>330.1467120864467</v>
+        <v>330.1480730268717</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30549,28 +30637,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.242244549719871</v>
+        <v>-0.2412672488231333</v>
       </c>
       <c r="J4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01019520741892233</v>
+        <v>0.01017371605562101</v>
       </c>
       <c r="M4" t="n">
-        <v>12.57847137625255</v>
+        <v>12.54467038023325</v>
       </c>
       <c r="N4" t="n">
-        <v>302.5989049298141</v>
+        <v>301.7041061110924</v>
       </c>
       <c r="O4" t="n">
-        <v>17.39537021537093</v>
+        <v>17.36963172065235</v>
       </c>
       <c r="P4" t="n">
-        <v>337.4550324618909</v>
+        <v>337.4443813863481</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30627,28 +30715,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6228678415475166</v>
+        <v>-0.6272610719886006</v>
       </c>
       <c r="J5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07814168421218626</v>
+        <v>0.07954811304127196</v>
       </c>
       <c r="M5" t="n">
-        <v>11.91180633488114</v>
+        <v>11.90147575697944</v>
       </c>
       <c r="N5" t="n">
-        <v>244.6100168226582</v>
+        <v>244.0492377992555</v>
       </c>
       <c r="O5" t="n">
-        <v>15.64001332552687</v>
+        <v>15.62207533585905</v>
       </c>
       <c r="P5" t="n">
-        <v>338.6726413712205</v>
+        <v>338.7202856422227</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30705,28 +30793,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8507094479436107</v>
+        <v>-0.8525910901077403</v>
       </c>
       <c r="J6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1144464865531982</v>
+        <v>0.1154971083491463</v>
       </c>
       <c r="M6" t="n">
-        <v>13.270511513492</v>
+        <v>13.2418021808564</v>
       </c>
       <c r="N6" t="n">
-        <v>295.7201944032861</v>
+        <v>294.86324617345</v>
       </c>
       <c r="O6" t="n">
-        <v>17.19651692649666</v>
+        <v>17.17158251802815</v>
       </c>
       <c r="P6" t="n">
-        <v>332.535299282819</v>
+        <v>332.5558941083606</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30783,28 +30871,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04089627638765117</v>
+        <v>0.03643990477775677</v>
       </c>
       <c r="J7" t="n">
+        <v>337</v>
+      </c>
+      <c r="K7" t="n">
         <v>336</v>
       </c>
-      <c r="K7" t="n">
-        <v>335</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0004578488091570021</v>
+        <v>0.0003653797792292357</v>
       </c>
       <c r="M7" t="n">
-        <v>11.12453162458239</v>
+        <v>11.11745907313409</v>
       </c>
       <c r="N7" t="n">
-        <v>196.8538149918516</v>
+        <v>196.4473301494455</v>
       </c>
       <c r="O7" t="n">
-        <v>14.03046025588083</v>
+        <v>14.01596697161653</v>
       </c>
       <c r="P7" t="n">
-        <v>312.5986051294882</v>
+        <v>312.6466456651628</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30861,28 +30949,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4409210296933253</v>
+        <v>-0.4465237100252455</v>
       </c>
       <c r="J8" t="n">
+        <v>337</v>
+      </c>
+      <c r="K8" t="n">
         <v>336</v>
       </c>
-      <c r="K8" t="n">
-        <v>335</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03505389803893777</v>
+        <v>0.03609081886996457</v>
       </c>
       <c r="M8" t="n">
-        <v>13.05755103280414</v>
+        <v>13.05252166674942</v>
       </c>
       <c r="N8" t="n">
-        <v>288.6399757862395</v>
+        <v>288.0649891462944</v>
       </c>
       <c r="O8" t="n">
-        <v>16.98940775266282</v>
+        <v>16.97247740155498</v>
       </c>
       <c r="P8" t="n">
-        <v>321.9783582968963</v>
+        <v>322.0387599369517</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30939,28 +31027,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3315587649724941</v>
+        <v>-0.3253484455228766</v>
       </c>
       <c r="J9" t="n">
+        <v>337</v>
+      </c>
+      <c r="K9" t="n">
         <v>336</v>
       </c>
-      <c r="K9" t="n">
-        <v>335</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03475882936661767</v>
+        <v>0.03363776191023271</v>
       </c>
       <c r="M9" t="n">
-        <v>9.774905042253145</v>
+        <v>9.768472913844137</v>
       </c>
       <c r="N9" t="n">
-        <v>162.3299494236093</v>
+        <v>162.1894282442354</v>
       </c>
       <c r="O9" t="n">
-        <v>12.74087710574156</v>
+        <v>12.73536133151452</v>
       </c>
       <c r="P9" t="n">
-        <v>327.2201600929199</v>
+        <v>327.1525941873098</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31017,28 +31105,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4596465405494438</v>
+        <v>-0.4618384615787478</v>
       </c>
       <c r="J10" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04578124727387389</v>
+        <v>0.04645393941447173</v>
       </c>
       <c r="M10" t="n">
-        <v>13.06770971495511</v>
+        <v>13.04086955290301</v>
       </c>
       <c r="N10" t="n">
-        <v>235.1071727067504</v>
+        <v>234.4420504784339</v>
       </c>
       <c r="O10" t="n">
-        <v>15.33320490656635</v>
+        <v>15.31150059525303</v>
       </c>
       <c r="P10" t="n">
-        <v>322.923094354641</v>
+        <v>322.9469651569835</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31095,28 +31183,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3268608882120742</v>
+        <v>-0.3178833432083635</v>
       </c>
       <c r="J11" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K11" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03232169300052445</v>
+        <v>0.0306765356962575</v>
       </c>
       <c r="M11" t="n">
-        <v>10.87214805992322</v>
+        <v>10.8772516567703</v>
       </c>
       <c r="N11" t="n">
-        <v>170.0590957592517</v>
+        <v>170.2681227569519</v>
       </c>
       <c r="O11" t="n">
-        <v>13.04067083240934</v>
+        <v>13.0486827977751</v>
       </c>
       <c r="P11" t="n">
-        <v>323.3396720600012</v>
+        <v>323.2418912641944</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31173,28 +31261,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4945775917525576</v>
+        <v>-0.4870873388141603</v>
       </c>
       <c r="J12" t="n">
+        <v>337</v>
+      </c>
+      <c r="K12" t="n">
         <v>336</v>
       </c>
-      <c r="K12" t="n">
-        <v>335</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1576010864240902</v>
+        <v>0.1534381467972272</v>
       </c>
       <c r="M12" t="n">
-        <v>6.853715606213453</v>
+        <v>6.867837948351043</v>
       </c>
       <c r="N12" t="n">
-        <v>69.52394267724439</v>
+        <v>69.81540215563916</v>
       </c>
       <c r="O12" t="n">
-        <v>8.338101862968838</v>
+        <v>8.35556115145112</v>
       </c>
       <c r="P12" t="n">
-        <v>337.9953620896605</v>
+        <v>337.9138709961449</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31251,28 +31339,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5663023353778607</v>
+        <v>-0.5751096938133623</v>
       </c>
       <c r="J13" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K13" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05531636887046509</v>
+        <v>0.05714927133331349</v>
       </c>
       <c r="M13" t="n">
-        <v>13.66016858258236</v>
+        <v>13.6813632212805</v>
       </c>
       <c r="N13" t="n">
-        <v>293.4622580196457</v>
+        <v>293.2624423141776</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1307401480393</v>
+        <v>17.12490707461438</v>
       </c>
       <c r="P13" t="n">
-        <v>340.4000739137039</v>
+        <v>340.495624332544</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31329,28 +31417,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4965113176166225</v>
+        <v>-0.4891399806792155</v>
       </c>
       <c r="J14" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K14" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05728505102761716</v>
+        <v>0.0558863004825555</v>
       </c>
       <c r="M14" t="n">
-        <v>11.67624632437962</v>
+        <v>11.67312517378561</v>
       </c>
       <c r="N14" t="n">
-        <v>215.0930235806063</v>
+        <v>214.9282954713414</v>
       </c>
       <c r="O14" t="n">
-        <v>14.66605003334594</v>
+        <v>14.66043299058188</v>
       </c>
       <c r="P14" t="n">
-        <v>341.519792365441</v>
+        <v>341.4391243029417</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31407,28 +31495,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.357472810928546</v>
+        <v>-0.3575045565132879</v>
       </c>
       <c r="J15" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K15" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0607368244397346</v>
+        <v>0.06108899676024704</v>
       </c>
       <c r="M15" t="n">
-        <v>7.353494290447101</v>
+        <v>7.331755078386294</v>
       </c>
       <c r="N15" t="n">
-        <v>105.065055198577</v>
+        <v>104.7514371293782</v>
       </c>
       <c r="O15" t="n">
-        <v>10.25012464307517</v>
+        <v>10.234814953353</v>
       </c>
       <c r="P15" t="n">
-        <v>344.8002781604803</v>
+        <v>344.8006239241092</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31485,28 +31573,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8975450764854436</v>
+        <v>-0.8923128329485022</v>
       </c>
       <c r="J16" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K16" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1889784635004989</v>
+        <v>0.1879004238395637</v>
       </c>
       <c r="M16" t="n">
-        <v>10.91531269980721</v>
+        <v>10.90566589072079</v>
       </c>
       <c r="N16" t="n">
-        <v>183.7072158638528</v>
+        <v>183.400745648036</v>
       </c>
       <c r="O16" t="n">
-        <v>13.55386350321755</v>
+        <v>13.54255314362975</v>
       </c>
       <c r="P16" t="n">
-        <v>352.4608123216584</v>
+        <v>352.4037466632028</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31563,28 +31651,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5178274953532843</v>
+        <v>-0.5178564192863587</v>
       </c>
       <c r="J17" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K17" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1184786524250032</v>
+        <v>0.1191161533826057</v>
       </c>
       <c r="M17" t="n">
-        <v>8.047164389341196</v>
+        <v>8.023301088702594</v>
       </c>
       <c r="N17" t="n">
-        <v>106.3318968573066</v>
+        <v>106.0144956684615</v>
       </c>
       <c r="O17" t="n">
-        <v>10.31173587992374</v>
+        <v>10.29633408881343</v>
       </c>
       <c r="P17" t="n">
-        <v>346.9515427494266</v>
+        <v>346.9518572442429</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31641,28 +31729,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6230144887417461</v>
+        <v>-0.6190497807755662</v>
       </c>
       <c r="J18" t="n">
+        <v>337</v>
+      </c>
+      <c r="K18" t="n">
         <v>336</v>
       </c>
-      <c r="K18" t="n">
-        <v>335</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1416954051152434</v>
+        <v>0.140737149805347</v>
       </c>
       <c r="M18" t="n">
-        <v>8.879169908700415</v>
+        <v>8.868204098702753</v>
       </c>
       <c r="N18" t="n">
-        <v>125.022705923334</v>
+        <v>124.7902470442557</v>
       </c>
       <c r="O18" t="n">
-        <v>11.18135528115148</v>
+        <v>11.17095551169441</v>
       </c>
       <c r="P18" t="n">
-        <v>350.8591599862804</v>
+        <v>350.8160254766328</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31719,28 +31807,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2210184078043883</v>
+        <v>-0.2171384227678671</v>
       </c>
       <c r="J19" t="n">
+        <v>337</v>
+      </c>
+      <c r="K19" t="n">
         <v>336</v>
       </c>
-      <c r="K19" t="n">
-        <v>335</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.0261389597706646</v>
+        <v>0.02536574973199857</v>
       </c>
       <c r="M19" t="n">
-        <v>7.658848824584137</v>
+        <v>7.651668240568814</v>
       </c>
       <c r="N19" t="n">
-        <v>96.77708000895089</v>
+        <v>96.62278156477549</v>
       </c>
       <c r="O19" t="n">
-        <v>9.837534244359757</v>
+        <v>9.829688782701897</v>
       </c>
       <c r="P19" t="n">
-        <v>344.032300631415</v>
+        <v>343.9900878749099</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31797,28 +31885,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2776004904593395</v>
+        <v>-0.2731709430771466</v>
       </c>
       <c r="J20" t="n">
+        <v>337</v>
+      </c>
+      <c r="K20" t="n">
         <v>336</v>
       </c>
-      <c r="K20" t="n">
-        <v>335</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.03423377206039713</v>
+        <v>0.0333298305285995</v>
       </c>
       <c r="M20" t="n">
-        <v>8.747426761022624</v>
+        <v>8.743554108779389</v>
       </c>
       <c r="N20" t="n">
-        <v>115.6018138902335</v>
+        <v>115.4320550319701</v>
       </c>
       <c r="O20" t="n">
-        <v>10.751828397544</v>
+        <v>10.74393107907762</v>
       </c>
       <c r="P20" t="n">
-        <v>348.0592881751843</v>
+        <v>348.011096390084</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31875,28 +31963,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2029121236783078</v>
+        <v>0.2002930798732541</v>
       </c>
       <c r="J21" t="n">
+        <v>337</v>
+      </c>
+      <c r="K21" t="n">
         <v>336</v>
       </c>
-      <c r="K21" t="n">
-        <v>335</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01924833967748774</v>
+        <v>0.01886431683481316</v>
       </c>
       <c r="M21" t="n">
-        <v>7.679770836684834</v>
+        <v>7.668704900325586</v>
       </c>
       <c r="N21" t="n">
-        <v>111.5549127901076</v>
+        <v>111.283836713412</v>
       </c>
       <c r="O21" t="n">
-        <v>10.56195591687958</v>
+        <v>10.54911544696578</v>
       </c>
       <c r="P21" t="n">
-        <v>334.456589167803</v>
+        <v>334.485083364914</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31953,28 +32041,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5085617244356649</v>
+        <v>-0.5054488995598925</v>
       </c>
       <c r="J22" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K22" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1438545057893765</v>
+        <v>0.1429512601121686</v>
       </c>
       <c r="M22" t="n">
-        <v>7.142999047493351</v>
+        <v>7.136103615159898</v>
       </c>
       <c r="N22" t="n">
-        <v>81.75555750815766</v>
+        <v>81.59755597437292</v>
       </c>
       <c r="O22" t="n">
-        <v>9.041877985692887</v>
+        <v>9.033136552403763</v>
       </c>
       <c r="P22" t="n">
-        <v>356.9525245845876</v>
+        <v>356.9185995846063</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32031,28 +32119,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3053480548329549</v>
+        <v>-0.309399360834553</v>
       </c>
       <c r="J23" t="n">
+        <v>337</v>
+      </c>
+      <c r="K23" t="n">
         <v>336</v>
       </c>
-      <c r="K23" t="n">
-        <v>335</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06341139205796387</v>
+        <v>0.06523809585389129</v>
       </c>
       <c r="M23" t="n">
-        <v>6.56144388844798</v>
+        <v>6.566078611843719</v>
       </c>
       <c r="N23" t="n">
-        <v>73.22827939686137</v>
+        <v>73.15613698171558</v>
       </c>
       <c r="O23" t="n">
-        <v>8.557352359045487</v>
+        <v>8.553136090447502</v>
       </c>
       <c r="P23" t="n">
-        <v>350.6304509134168</v>
+        <v>350.674527576642</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32090,7 +32178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X337"/>
+  <dimension ref="A1:X338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73007,6 +73095,128 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-37.756996755659834,174.83000440963045</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-37.75627040845195,174.83001040060537</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-37.755596596717595,174.829696895996</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-37.75485741342081,174.8297247860215</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-37.75413464465875,174.82959390924788</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-37.75344054724797,174.82936399075825</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-37.752741704266626,174.82918359547395</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-37.752128680620814,174.82862959685957</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-37.75138776968941,174.8286273219521</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-37.75076326198062,174.8281296078919</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-37.75009793065992,174.82779748139055</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-37.74934071935079,174.8278269731206</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-37.748748911535394,174.82722632568033</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-37.74805413669695,174.82702108896976</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-37.7473832039244,174.82672093530087</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>-37.74669407413428,174.82649022189472</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>-37.74604255831149,174.82612386628284</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>-37.745385378738575,174.82580761573084</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>-37.74470422477739,174.82560158374562</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>-37.74398316156374,174.82560618542234</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>-37.743303318799875,174.82530412578987</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>-37.74258076155414,174.8252902387004</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X338"/>
+  <dimension ref="A1:X340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26739,6 +26739,162 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="C339" t="n">
+        <v>323.12</v>
+      </c>
+      <c r="D339" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="E339" t="n">
+        <v>323.69</v>
+      </c>
+      <c r="F339" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="G339" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="H339" t="n">
+        <v>307.49</v>
+      </c>
+      <c r="I339" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="J339" t="n">
+        <v>314.76</v>
+      </c>
+      <c r="K339" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="L339" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="M339" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="N339" t="n">
+        <v>341.22</v>
+      </c>
+      <c r="O339" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="P339" t="n">
+        <v>338.69</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="R339" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="S339" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="T339" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="U339" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="V339" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="W339" t="n">
+        <v>336.94</v>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="C340" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="D340" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="E340" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="F340" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="G340" t="n">
+        <v>316.91</v>
+      </c>
+      <c r="H340" t="n">
+        <v>313.87</v>
+      </c>
+      <c r="I340" t="n">
+        <v>327.82</v>
+      </c>
+      <c r="J340" t="n">
+        <v>320.72</v>
+      </c>
+      <c r="K340" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="L340" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="M340" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="N340" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="O340" t="n">
+        <v>341.15</v>
+      </c>
+      <c r="P340" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>330.62</v>
+      </c>
+      <c r="R340" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="S340" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="T340" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="U340" t="n">
+        <v>331</v>
+      </c>
+      <c r="V340" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="W340" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26750,7 +26906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30313,6 +30469,26 @@
       </c>
       <c r="B356" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -30481,28 +30657,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4447749426331249</v>
+        <v>-0.4358781696298039</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1072515381296236</v>
+        <v>0.1041574648697791</v>
       </c>
       <c r="M2" t="n">
-        <v>7.177426241169683</v>
+        <v>7.182499160828719</v>
       </c>
       <c r="N2" t="n">
-        <v>87.71219827086303</v>
+        <v>87.55120995173937</v>
       </c>
       <c r="O2" t="n">
-        <v>9.365479073216864</v>
+        <v>9.356880353608213</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4071928054701</v>
+        <v>340.309986091254</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30559,28 +30735,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3785573796844496</v>
+        <v>-0.3741980178935362</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03588019474058946</v>
+        <v>0.03547523531796959</v>
       </c>
       <c r="M3" t="n">
-        <v>10.44234175052395</v>
+        <v>10.40691675566758</v>
       </c>
       <c r="N3" t="n">
-        <v>205.3770249821788</v>
+        <v>204.251862242459</v>
       </c>
       <c r="O3" t="n">
-        <v>14.33098129864731</v>
+        <v>14.29167107942451</v>
       </c>
       <c r="P3" t="n">
-        <v>330.1480730268717</v>
+        <v>330.1005679447951</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30637,28 +30813,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2412672488231333</v>
+        <v>-0.238353305538535</v>
       </c>
       <c r="J4" t="n">
+        <v>339</v>
+      </c>
+      <c r="K4" t="n">
         <v>337</v>
       </c>
-      <c r="K4" t="n">
-        <v>335</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01017371605562101</v>
+        <v>0.0100475671625766</v>
       </c>
       <c r="M4" t="n">
-        <v>12.54467038023325</v>
+        <v>12.48129356913305</v>
       </c>
       <c r="N4" t="n">
-        <v>301.7041061110924</v>
+        <v>299.9519602576146</v>
       </c>
       <c r="O4" t="n">
-        <v>17.36963172065235</v>
+        <v>17.31912123225698</v>
       </c>
       <c r="P4" t="n">
-        <v>337.4443813863481</v>
+        <v>337.4125769125652</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30715,28 +30891,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6272610719886006</v>
+        <v>-0.6215340967545591</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07954811304127196</v>
+        <v>0.07901028314032921</v>
       </c>
       <c r="M5" t="n">
-        <v>11.90147575697944</v>
+        <v>11.85671311420426</v>
       </c>
       <c r="N5" t="n">
-        <v>244.0492377992555</v>
+        <v>242.8171367461154</v>
       </c>
       <c r="O5" t="n">
-        <v>15.62207533585905</v>
+        <v>15.58259082264934</v>
       </c>
       <c r="P5" t="n">
-        <v>338.7202856422227</v>
+        <v>338.6580609182042</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30793,28 +30969,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8525910901077403</v>
+        <v>-0.8432012404906671</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K6" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1154971083491463</v>
+        <v>0.1142922563177033</v>
       </c>
       <c r="M6" t="n">
-        <v>13.2418021808564</v>
+        <v>13.20363172134094</v>
       </c>
       <c r="N6" t="n">
-        <v>294.86324617345</v>
+        <v>293.5677405889813</v>
       </c>
       <c r="O6" t="n">
-        <v>17.17158251802815</v>
+        <v>17.1338186225074</v>
       </c>
       <c r="P6" t="n">
-        <v>332.5558941083606</v>
+        <v>332.4529441873087</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30871,28 +31047,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03643990477775677</v>
+        <v>0.03729306526833039</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K7" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003653797792292357</v>
+        <v>0.0003871410693533361</v>
       </c>
       <c r="M7" t="n">
-        <v>11.11745907313409</v>
+        <v>11.06618871354269</v>
       </c>
       <c r="N7" t="n">
-        <v>196.4473301494455</v>
+        <v>195.3265018375978</v>
       </c>
       <c r="O7" t="n">
-        <v>14.01596697161653</v>
+        <v>13.97592579536675</v>
       </c>
       <c r="P7" t="n">
-        <v>312.6466456651628</v>
+        <v>312.6374184990931</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30949,28 +31125,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4465237100252455</v>
+        <v>-0.4460318672742054</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03609081886996457</v>
+        <v>0.0364180370500703</v>
       </c>
       <c r="M8" t="n">
-        <v>13.05252166674942</v>
+        <v>12.99379124548088</v>
       </c>
       <c r="N8" t="n">
-        <v>288.0649891462944</v>
+        <v>286.42195407015</v>
       </c>
       <c r="O8" t="n">
-        <v>16.97247740155498</v>
+        <v>16.92400526087575</v>
       </c>
       <c r="P8" t="n">
-        <v>322.0387599369517</v>
+        <v>322.0334293575354</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31027,28 +31203,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3253484455228766</v>
+        <v>-0.3141409520952809</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03363776191023271</v>
+        <v>0.031685986863497</v>
       </c>
       <c r="M9" t="n">
-        <v>9.768472913844137</v>
+        <v>9.751288118972257</v>
       </c>
       <c r="N9" t="n">
-        <v>162.1894282442354</v>
+        <v>161.7979638163486</v>
       </c>
       <c r="O9" t="n">
-        <v>12.73536133151452</v>
+        <v>12.71998285440466</v>
       </c>
       <c r="P9" t="n">
-        <v>327.1525941873098</v>
+        <v>327.0304811480823</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31105,28 +31281,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4618384615787478</v>
+        <v>-0.4538839658488455</v>
       </c>
       <c r="J10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K10" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04645393941447173</v>
+        <v>0.04538406362986713</v>
       </c>
       <c r="M10" t="n">
-        <v>13.04086955290301</v>
+        <v>12.99999300465253</v>
       </c>
       <c r="N10" t="n">
-        <v>234.4420504784339</v>
+        <v>233.3785784345315</v>
       </c>
       <c r="O10" t="n">
-        <v>15.31150059525303</v>
+        <v>15.2767332383115</v>
       </c>
       <c r="P10" t="n">
-        <v>322.9469651569835</v>
+        <v>322.860186336897</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31183,28 +31359,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3178833432083635</v>
+        <v>-0.3020239848979709</v>
       </c>
       <c r="J11" t="n">
+        <v>339</v>
+      </c>
+      <c r="K11" t="n">
         <v>337</v>
       </c>
-      <c r="K11" t="n">
-        <v>335</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0306765356962575</v>
+        <v>0.02791125773155956</v>
       </c>
       <c r="M11" t="n">
-        <v>10.8772516567703</v>
+        <v>10.87914973600072</v>
       </c>
       <c r="N11" t="n">
-        <v>170.2681227569519</v>
+        <v>170.4094856612285</v>
       </c>
       <c r="O11" t="n">
-        <v>13.0486827977751</v>
+        <v>13.05409842391379</v>
       </c>
       <c r="P11" t="n">
-        <v>323.2418912641944</v>
+        <v>323.0689056303218</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31261,28 +31437,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4870873388141603</v>
+        <v>-0.4759577304254438</v>
       </c>
       <c r="J12" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K12" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1534381467972272</v>
+        <v>0.147957548635587</v>
       </c>
       <c r="M12" t="n">
-        <v>6.867837948351043</v>
+        <v>6.878022015415927</v>
       </c>
       <c r="N12" t="n">
-        <v>69.81540215563916</v>
+        <v>69.9899748171137</v>
       </c>
       <c r="O12" t="n">
-        <v>8.35556115145112</v>
+        <v>8.366001124618244</v>
       </c>
       <c r="P12" t="n">
-        <v>337.9138709961449</v>
+        <v>337.7926167871781</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31339,28 +31515,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5751096938133623</v>
+        <v>-0.5773921050693168</v>
       </c>
       <c r="J13" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K13" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05714927133331349</v>
+        <v>0.05821052226597867</v>
       </c>
       <c r="M13" t="n">
-        <v>13.6813632212805</v>
+        <v>13.62339788315016</v>
       </c>
       <c r="N13" t="n">
-        <v>293.2624423141776</v>
+        <v>291.5868598533543</v>
       </c>
       <c r="O13" t="n">
-        <v>17.12490707461438</v>
+        <v>17.07591461249893</v>
       </c>
       <c r="P13" t="n">
-        <v>340.495624332544</v>
+        <v>340.5204023752797</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31417,28 +31593,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4891399806792155</v>
+        <v>-0.4759821913313878</v>
       </c>
       <c r="J14" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K14" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0558863004825555</v>
+        <v>0.05348620271526106</v>
       </c>
       <c r="M14" t="n">
-        <v>11.67312517378561</v>
+        <v>11.65996938510323</v>
       </c>
       <c r="N14" t="n">
-        <v>214.9282954713414</v>
+        <v>214.4304063242031</v>
       </c>
       <c r="O14" t="n">
-        <v>14.66043299058188</v>
+        <v>14.64344243421618</v>
       </c>
       <c r="P14" t="n">
-        <v>341.4391243029417</v>
+        <v>341.2949208239077</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31495,28 +31671,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3575045565132879</v>
+        <v>-0.3513537958577175</v>
       </c>
       <c r="J15" t="n">
+        <v>339</v>
+      </c>
+      <c r="K15" t="n">
         <v>337</v>
       </c>
-      <c r="K15" t="n">
-        <v>335</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.06108899676024704</v>
+        <v>0.05969692289302986</v>
       </c>
       <c r="M15" t="n">
-        <v>7.331755078386294</v>
+        <v>7.310783831568627</v>
       </c>
       <c r="N15" t="n">
-        <v>104.7514371293782</v>
+        <v>104.3012716776999</v>
       </c>
       <c r="O15" t="n">
-        <v>10.234814953353</v>
+        <v>10.21279940455602</v>
       </c>
       <c r="P15" t="n">
-        <v>344.8006239241092</v>
+        <v>344.7335280229329</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31573,28 +31749,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8923128329485022</v>
+        <v>-0.8830569417360509</v>
       </c>
       <c r="J16" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K16" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1879004238395637</v>
+        <v>0.1861883978728104</v>
       </c>
       <c r="M16" t="n">
-        <v>10.90566589072079</v>
+        <v>10.88113474491819</v>
       </c>
       <c r="N16" t="n">
-        <v>183.400745648036</v>
+        <v>182.7131439782385</v>
       </c>
       <c r="O16" t="n">
-        <v>13.54255314362975</v>
+        <v>13.51714259665254</v>
       </c>
       <c r="P16" t="n">
-        <v>352.4037466632028</v>
+        <v>352.302654914482</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31651,28 +31827,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5178564192863587</v>
+        <v>-0.5193564575360052</v>
       </c>
       <c r="J17" t="n">
+        <v>339</v>
+      </c>
+      <c r="K17" t="n">
         <v>337</v>
       </c>
-      <c r="K17" t="n">
-        <v>335</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1191161533826057</v>
+        <v>0.1209548336646941</v>
       </c>
       <c r="M17" t="n">
-        <v>8.023301088702594</v>
+        <v>7.984039705604521</v>
       </c>
       <c r="N17" t="n">
-        <v>106.0144956684615</v>
+        <v>105.4060893440688</v>
       </c>
       <c r="O17" t="n">
-        <v>10.29633408881343</v>
+        <v>10.26674677510207</v>
       </c>
       <c r="P17" t="n">
-        <v>346.9518572442429</v>
+        <v>346.9682005370314</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31729,28 +31905,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6190497807755662</v>
+        <v>-0.6137289912869097</v>
       </c>
       <c r="J18" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K18" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L18" t="n">
-        <v>0.140737149805347</v>
+        <v>0.1399286712000029</v>
       </c>
       <c r="M18" t="n">
-        <v>8.868204098702753</v>
+        <v>8.83630404224882</v>
       </c>
       <c r="N18" t="n">
-        <v>124.7902470442557</v>
+        <v>124.2098392434804</v>
       </c>
       <c r="O18" t="n">
-        <v>11.17095551169441</v>
+        <v>11.14494680307988</v>
       </c>
       <c r="P18" t="n">
-        <v>350.8160254766328</v>
+        <v>350.7580643994604</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31807,28 +31983,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2171384227678671</v>
+        <v>-0.2127164607378787</v>
       </c>
       <c r="J19" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K19" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02536574973199857</v>
+        <v>0.02461929469278956</v>
       </c>
       <c r="M19" t="n">
-        <v>7.651668240568814</v>
+        <v>7.62403373393401</v>
       </c>
       <c r="N19" t="n">
-        <v>96.62278156477549</v>
+        <v>96.17799333700228</v>
       </c>
       <c r="O19" t="n">
-        <v>9.829688782701897</v>
+        <v>9.807037949197621</v>
       </c>
       <c r="P19" t="n">
-        <v>343.9900878749099</v>
+        <v>343.9419222773947</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31885,28 +32061,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2731709430771466</v>
+        <v>-0.268036609043137</v>
       </c>
       <c r="J20" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K20" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0333298305285995</v>
+        <v>0.03245092526543392</v>
       </c>
       <c r="M20" t="n">
-        <v>8.743554108779389</v>
+        <v>8.717291965322316</v>
       </c>
       <c r="N20" t="n">
-        <v>115.4320550319701</v>
+        <v>114.9235701743544</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74393107907762</v>
+        <v>10.72024114347968</v>
       </c>
       <c r="P20" t="n">
-        <v>348.011096390084</v>
+        <v>347.9551719801658</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31963,28 +32139,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2002930798732541</v>
+        <v>0.1923761367546532</v>
       </c>
       <c r="J21" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K21" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01886431683481316</v>
+        <v>0.01758472446362669</v>
       </c>
       <c r="M21" t="n">
-        <v>7.668704900325586</v>
+        <v>7.659477290828494</v>
       </c>
       <c r="N21" t="n">
-        <v>111.283836713412</v>
+        <v>110.9269057241249</v>
       </c>
       <c r="O21" t="n">
-        <v>10.54911544696578</v>
+        <v>10.53218428077125</v>
       </c>
       <c r="P21" t="n">
-        <v>334.485083364914</v>
+        <v>334.5713577212334</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32041,28 +32217,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5054488995598925</v>
+        <v>-0.5007032443344002</v>
       </c>
       <c r="J22" t="n">
+        <v>339</v>
+      </c>
+      <c r="K22" t="n">
         <v>337</v>
       </c>
-      <c r="K22" t="n">
-        <v>335</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1429512601121686</v>
+        <v>0.1419000917908831</v>
       </c>
       <c r="M22" t="n">
-        <v>7.136103615159898</v>
+        <v>7.115556442400473</v>
       </c>
       <c r="N22" t="n">
-        <v>81.59755597437292</v>
+        <v>81.2403763706567</v>
       </c>
       <c r="O22" t="n">
-        <v>9.033136552403763</v>
+        <v>9.013344349943406</v>
       </c>
       <c r="P22" t="n">
-        <v>356.9185995846063</v>
+        <v>356.8668143372377</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32119,28 +32295,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.309399360834553</v>
+        <v>-0.3159219907572758</v>
       </c>
       <c r="J23" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K23" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06523809585389129</v>
+        <v>0.06841326329841191</v>
       </c>
       <c r="M23" t="n">
-        <v>6.566078611843719</v>
+        <v>6.565782636260519</v>
       </c>
       <c r="N23" t="n">
-        <v>73.15613698171558</v>
+        <v>72.91513199641767</v>
       </c>
       <c r="O23" t="n">
-        <v>8.553136090447502</v>
+        <v>8.539035776738359</v>
       </c>
       <c r="P23" t="n">
-        <v>350.674527576642</v>
+        <v>350.7455992064857</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32178,7 +32354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X338"/>
+  <dimension ref="A1:X340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73217,6 +73393,250 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-37.756999350781896,174.82998862919197</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-37.75627620179778,174.82997517278972</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-37.755598479072766,174.8296854498304</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-37.75487578770897,174.82962472292033</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-37.75415328729707,174.8295076210994</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-37.75345539025403,174.82929922571728</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-37.7527591555331,174.829107849683</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-37.752128147196586,174.82863188331203</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-37.75140761303673,174.8285428819637</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-37.75076382855149,174.82812721549215</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-37.75009558701359,174.8278069024523</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-37.749367707602495,174.8277227567205</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-37.74874910709945,174.82722557049377</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-37.7480684143625,174.82696643910467</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-37.747385619213645,174.82671190182572</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>-37.7466942197443,174.82648968497983</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>-37.74604290777242,174.82612257769688</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>-37.74538483412888,174.82581013383856</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>-37.74470415765316,174.82560202968523</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>-37.743982137533415,174.82561344729748</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>-37.74330482674225,174.8252940917761</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>-37.74258318442412,174.82527476472956</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-37.756996298771924,174.83000718787653</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-37.75627938173714,174.82995583638365</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-37.75559791253881,174.82968889479292</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-37.75488997950513,174.8295474365773</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-37.75416972967396,174.82943151666655</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-37.75346810923307,174.8292437283794</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-37.75277517550251,174.82903831610383</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-37.752125048255046,174.82864516651136</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-37.75142285350541,174.82847802853834</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-37.75075507245095,174.82816418893896</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-37.750083599385725,174.82785509063189</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-37.749386398171055,174.82765058196227</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-37.74874256967026,174.82725081529904</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-37.74807055460213,174.82695824701253</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-37.74737575677832,174.8267487885121</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>-37.74668641504408,174.82651846361497</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>-37.746029686491156,174.8261713291909</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>-37.745372710629695,174.82586618909633</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>-37.74469385406351,174.8256704814</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>-37.74397645021843,174.8256537786309</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>-37.74329785669044,174.8253404712137</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>-37.74258257434913,174.82527866105326</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X340"/>
+  <dimension ref="A1:X341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26895,6 +26895,84 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>335.69</v>
+      </c>
+      <c r="C341" t="n">
+        <v>325.71</v>
+      </c>
+      <c r="D341" t="n">
+        <v>333.89</v>
+      </c>
+      <c r="E341" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="F341" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="G341" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="H341" t="n">
+        <v>315.36</v>
+      </c>
+      <c r="I341" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="J341" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="K341" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="L341" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="M341" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="N341" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="O341" t="n">
+        <v>341.69</v>
+      </c>
+      <c r="P341" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="R341" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="S341" t="n">
+        <v>339.68</v>
+      </c>
+      <c r="T341" t="n">
+        <v>342.03</v>
+      </c>
+      <c r="U341" t="n">
+        <v>332.8</v>
+      </c>
+      <c r="V341" t="n">
+        <v>346.17</v>
+      </c>
+      <c r="W341" t="n">
+        <v>338.53</v>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26906,7 +26984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30489,6 +30567,16 @@
       </c>
       <c r="B358" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -30657,28 +30745,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4358781696298039</v>
+        <v>-0.4319682787625641</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1041574648697791</v>
+        <v>0.1028779438570473</v>
       </c>
       <c r="M2" t="n">
-        <v>7.182499160828719</v>
+        <v>7.182145692397158</v>
       </c>
       <c r="N2" t="n">
-        <v>87.55120995173937</v>
+        <v>87.43168176038991</v>
       </c>
       <c r="O2" t="n">
-        <v>9.356880353608213</v>
+        <v>9.350490990337882</v>
       </c>
       <c r="P2" t="n">
-        <v>340.309986091254</v>
+        <v>340.2671987547194</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30735,28 +30823,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3741980178935362</v>
+        <v>-0.3710931298677224</v>
       </c>
       <c r="J3" t="n">
+        <v>340</v>
+      </c>
+      <c r="K3" t="n">
         <v>339</v>
       </c>
-      <c r="K3" t="n">
-        <v>338</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03547523531796959</v>
+        <v>0.03509240119541401</v>
       </c>
       <c r="M3" t="n">
-        <v>10.40691675566758</v>
+        <v>10.39513027749891</v>
       </c>
       <c r="N3" t="n">
-        <v>204.251862242459</v>
+        <v>203.7377434821077</v>
       </c>
       <c r="O3" t="n">
-        <v>14.29167107942451</v>
+        <v>14.27367309006717</v>
       </c>
       <c r="P3" t="n">
-        <v>330.1005679447951</v>
+        <v>330.0666856474598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30813,28 +30901,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.238353305538535</v>
+        <v>-0.2367799317650955</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0100475671625766</v>
+        <v>0.009973482805091693</v>
       </c>
       <c r="M4" t="n">
-        <v>12.48129356913305</v>
+        <v>12.45030894737256</v>
       </c>
       <c r="N4" t="n">
-        <v>299.9519602576146</v>
+        <v>299.087218287976</v>
       </c>
       <c r="O4" t="n">
-        <v>17.31912123225698</v>
+        <v>17.29413826381575</v>
       </c>
       <c r="P4" t="n">
-        <v>337.4125769125652</v>
+        <v>337.3953775229668</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30891,28 +30979,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6215340967545591</v>
+        <v>-0.6162558007247384</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07901028314032921</v>
+        <v>0.07812430666191605</v>
       </c>
       <c r="M5" t="n">
-        <v>11.85671311420426</v>
+        <v>11.84543748732206</v>
       </c>
       <c r="N5" t="n">
-        <v>242.8171367461154</v>
+        <v>242.3523316011479</v>
       </c>
       <c r="O5" t="n">
-        <v>15.58259082264934</v>
+        <v>15.56766943383459</v>
       </c>
       <c r="P5" t="n">
-        <v>338.6580609182042</v>
+        <v>338.6006439478222</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30969,28 +31057,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8432012404906671</v>
+        <v>-0.8352421026312766</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1142922563177033</v>
+        <v>0.1127772190203578</v>
       </c>
       <c r="M6" t="n">
-        <v>13.20363172134094</v>
+        <v>13.19878811079678</v>
       </c>
       <c r="N6" t="n">
-        <v>293.5677405889813</v>
+        <v>293.2684860110779</v>
       </c>
       <c r="O6" t="n">
-        <v>17.1338186225074</v>
+        <v>17.12508353296643</v>
       </c>
       <c r="P6" t="n">
-        <v>332.4529441873087</v>
+        <v>332.3655668750558</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31047,28 +31135,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03729306526833039</v>
+        <v>0.03973286542552415</v>
       </c>
       <c r="J7" t="n">
+        <v>340</v>
+      </c>
+      <c r="K7" t="n">
         <v>339</v>
       </c>
-      <c r="K7" t="n">
-        <v>338</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0003871410693533361</v>
+        <v>0.000441874403706688</v>
       </c>
       <c r="M7" t="n">
-        <v>11.06618871354269</v>
+        <v>11.04475844757562</v>
       </c>
       <c r="N7" t="n">
-        <v>195.3265018375978</v>
+        <v>194.8058176464477</v>
       </c>
       <c r="O7" t="n">
-        <v>13.97592579536675</v>
+        <v>13.95728546840136</v>
       </c>
       <c r="P7" t="n">
-        <v>312.6374184990931</v>
+        <v>312.6110363625081</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31125,28 +31213,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4460318672742054</v>
+        <v>-0.4431681150952076</v>
       </c>
       <c r="J8" t="n">
+        <v>340</v>
+      </c>
+      <c r="K8" t="n">
         <v>339</v>
       </c>
-      <c r="K8" t="n">
-        <v>338</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0364180370500703</v>
+        <v>0.03616185898098523</v>
       </c>
       <c r="M8" t="n">
-        <v>12.99379124548088</v>
+        <v>12.96809194662269</v>
       </c>
       <c r="N8" t="n">
-        <v>286.42195407015</v>
+        <v>285.6536495918791</v>
       </c>
       <c r="O8" t="n">
-        <v>16.92400526087575</v>
+        <v>16.90129135870627</v>
       </c>
       <c r="P8" t="n">
-        <v>322.0334293575354</v>
+        <v>322.0024609146377</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31203,28 +31291,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3141409520952809</v>
+        <v>-0.3094422508627097</v>
       </c>
       <c r="J9" t="n">
+        <v>340</v>
+      </c>
+      <c r="K9" t="n">
         <v>339</v>
       </c>
-      <c r="K9" t="n">
-        <v>338</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.031685986863497</v>
+        <v>0.03091156291554775</v>
       </c>
       <c r="M9" t="n">
-        <v>9.751288118972257</v>
+        <v>9.739913182873945</v>
       </c>
       <c r="N9" t="n">
-        <v>161.7979638163486</v>
+        <v>161.523119382231</v>
       </c>
       <c r="O9" t="n">
-        <v>12.71998285440466</v>
+        <v>12.70917461451494</v>
       </c>
       <c r="P9" t="n">
-        <v>327.0304811480823</v>
+        <v>326.9792062579968</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31281,28 +31369,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4538839658488455</v>
+        <v>-0.4480766386951652</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K10" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04538406362986713</v>
+        <v>0.04447151246181225</v>
       </c>
       <c r="M10" t="n">
-        <v>12.99999300465253</v>
+        <v>12.98820254336426</v>
       </c>
       <c r="N10" t="n">
-        <v>233.3785784345315</v>
+        <v>232.9936764949317</v>
       </c>
       <c r="O10" t="n">
-        <v>15.2767332383115</v>
+        <v>15.26413038777289</v>
       </c>
       <c r="P10" t="n">
-        <v>322.860186336897</v>
+        <v>322.7967480008135</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31359,28 +31447,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3020239848979709</v>
+        <v>-0.2953895192956951</v>
       </c>
       <c r="J11" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K11" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02791125773155956</v>
+        <v>0.02682131318830927</v>
       </c>
       <c r="M11" t="n">
-        <v>10.87914973600072</v>
+        <v>10.87497357035177</v>
       </c>
       <c r="N11" t="n">
-        <v>170.4094856612285</v>
+        <v>170.3092977113508</v>
       </c>
       <c r="O11" t="n">
-        <v>13.05409842391379</v>
+        <v>13.05026044611182</v>
       </c>
       <c r="P11" t="n">
-        <v>323.0689056303218</v>
+        <v>322.9964254665178</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31437,28 +31525,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4759577304254438</v>
+        <v>-0.4721308332919808</v>
       </c>
       <c r="J12" t="n">
+        <v>340</v>
+      </c>
+      <c r="K12" t="n">
         <v>339</v>
       </c>
-      <c r="K12" t="n">
-        <v>338</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.147957548635587</v>
+        <v>0.1464239800810682</v>
       </c>
       <c r="M12" t="n">
-        <v>6.878022015415927</v>
+        <v>6.875088820447857</v>
       </c>
       <c r="N12" t="n">
-        <v>69.9899748171137</v>
+        <v>69.91779894280347</v>
       </c>
       <c r="O12" t="n">
-        <v>8.366001124618244</v>
+        <v>8.361686369555095</v>
       </c>
       <c r="P12" t="n">
-        <v>337.7926167871781</v>
+        <v>337.7508555173773</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31515,28 +31603,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5773921050693168</v>
+        <v>-0.5761313416815367</v>
       </c>
       <c r="J13" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05821052226597867</v>
+        <v>0.05829103369593736</v>
       </c>
       <c r="M13" t="n">
-        <v>13.62339788315016</v>
+        <v>13.58672266528024</v>
       </c>
       <c r="N13" t="n">
-        <v>291.5868598533543</v>
+        <v>290.7258124636895</v>
       </c>
       <c r="O13" t="n">
-        <v>17.07591461249893</v>
+        <v>17.05068363625604</v>
       </c>
       <c r="P13" t="n">
-        <v>340.5204023752797</v>
+        <v>340.5066824347194</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31593,28 +31681,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4759821913313878</v>
+        <v>-0.4701301087488947</v>
       </c>
       <c r="J14" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K14" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05348620271526106</v>
+        <v>0.05246364435646333</v>
       </c>
       <c r="M14" t="n">
-        <v>11.65996938510323</v>
+        <v>11.65053277981733</v>
       </c>
       <c r="N14" t="n">
-        <v>214.4304063242031</v>
+        <v>214.1045861563703</v>
       </c>
       <c r="O14" t="n">
-        <v>14.64344243421618</v>
+        <v>14.63231308291243</v>
       </c>
       <c r="P14" t="n">
-        <v>341.2949208239077</v>
+        <v>341.2306827806537</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31671,28 +31759,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3513537958577175</v>
+        <v>-0.3478236417960364</v>
       </c>
       <c r="J15" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K15" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05969692289302986</v>
+        <v>0.05883546497441716</v>
       </c>
       <c r="M15" t="n">
-        <v>7.310783831568627</v>
+        <v>7.30233394553191</v>
       </c>
       <c r="N15" t="n">
-        <v>104.3012716776999</v>
+        <v>104.1070647371242</v>
       </c>
       <c r="O15" t="n">
-        <v>10.21279940455602</v>
+        <v>10.2032869575017</v>
       </c>
       <c r="P15" t="n">
-        <v>344.7335280229329</v>
+        <v>344.6949618203203</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31749,28 +31837,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8830569417360509</v>
+        <v>-0.8787390352533574</v>
       </c>
       <c r="J16" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K16" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1861883978728104</v>
+        <v>0.1854463378789706</v>
       </c>
       <c r="M16" t="n">
-        <v>10.88113474491819</v>
+        <v>10.86756416962147</v>
       </c>
       <c r="N16" t="n">
-        <v>182.7131439782385</v>
+        <v>182.3421638825824</v>
       </c>
       <c r="O16" t="n">
-        <v>13.51714259665254</v>
+        <v>13.50341304569265</v>
       </c>
       <c r="P16" t="n">
-        <v>352.302654914482</v>
+        <v>352.2554180682096</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31827,28 +31915,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5193564575360052</v>
+        <v>-0.5200002214402277</v>
       </c>
       <c r="J17" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K17" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1209548336646941</v>
+        <v>0.1218384305016427</v>
       </c>
       <c r="M17" t="n">
-        <v>7.984039705604521</v>
+        <v>7.963942270654935</v>
       </c>
       <c r="N17" t="n">
-        <v>105.4060893440688</v>
+        <v>105.0980506666897</v>
       </c>
       <c r="O17" t="n">
-        <v>10.26674677510207</v>
+        <v>10.25173403218644</v>
       </c>
       <c r="P17" t="n">
-        <v>346.9682005370314</v>
+        <v>346.975221593641</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31905,28 +31993,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6137289912869097</v>
+        <v>-0.6124354491850876</v>
       </c>
       <c r="J18" t="n">
+        <v>340</v>
+      </c>
+      <c r="K18" t="n">
         <v>339</v>
       </c>
-      <c r="K18" t="n">
-        <v>338</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1399286712000029</v>
+        <v>0.1401101742772924</v>
       </c>
       <c r="M18" t="n">
-        <v>8.83630404224882</v>
+        <v>8.815244794825372</v>
       </c>
       <c r="N18" t="n">
-        <v>124.2098392434804</v>
+        <v>123.8587809118416</v>
       </c>
       <c r="O18" t="n">
-        <v>11.14494680307988</v>
+        <v>11.12918599502415</v>
       </c>
       <c r="P18" t="n">
-        <v>350.7580643994604</v>
+        <v>350.7439485351377</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31983,28 +32071,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2127164607378787</v>
+        <v>-0.2119461473880393</v>
       </c>
       <c r="J19" t="n">
+        <v>340</v>
+      </c>
+      <c r="K19" t="n">
         <v>339</v>
       </c>
-      <c r="K19" t="n">
-        <v>338</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02461929469278956</v>
+        <v>0.02458422360987966</v>
       </c>
       <c r="M19" t="n">
-        <v>7.62403373393401</v>
+        <v>7.604594964134698</v>
       </c>
       <c r="N19" t="n">
-        <v>96.17799333700228</v>
+        <v>95.89972328627427</v>
       </c>
       <c r="O19" t="n">
-        <v>9.807037949197621</v>
+        <v>9.792840409517265</v>
       </c>
       <c r="P19" t="n">
-        <v>343.9419222773947</v>
+        <v>343.9335161816697</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32061,28 +32149,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.268036609043137</v>
+        <v>-0.2673803766102785</v>
       </c>
       <c r="J20" t="n">
+        <v>340</v>
+      </c>
+      <c r="K20" t="n">
         <v>339</v>
       </c>
-      <c r="K20" t="n">
-        <v>338</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.03245092526543392</v>
+        <v>0.03247963369488871</v>
       </c>
       <c r="M20" t="n">
-        <v>8.717291965322316</v>
+        <v>8.694811210157514</v>
       </c>
       <c r="N20" t="n">
-        <v>114.9235701743544</v>
+        <v>114.5885112260953</v>
       </c>
       <c r="O20" t="n">
-        <v>10.72024114347968</v>
+        <v>10.70460233853156</v>
       </c>
       <c r="P20" t="n">
-        <v>347.9551719801658</v>
+        <v>347.9480108000439</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32139,28 +32227,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1923761367546532</v>
+        <v>0.1885019831661827</v>
       </c>
       <c r="J21" t="n">
+        <v>340</v>
+      </c>
+      <c r="K21" t="n">
         <v>339</v>
       </c>
-      <c r="K21" t="n">
-        <v>338</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01758472446362669</v>
+        <v>0.01697214482812803</v>
       </c>
       <c r="M21" t="n">
-        <v>7.659477290828494</v>
+        <v>7.654632617235983</v>
       </c>
       <c r="N21" t="n">
-        <v>110.9269057241249</v>
+        <v>110.7373088366337</v>
       </c>
       <c r="O21" t="n">
-        <v>10.53218428077125</v>
+        <v>10.52317959728112</v>
       </c>
       <c r="P21" t="n">
-        <v>334.5713577212334</v>
+        <v>334.6136346802463</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32217,28 +32305,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5007032443344002</v>
+        <v>-0.4992650210945796</v>
       </c>
       <c r="J22" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K22" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1419000917908831</v>
+        <v>0.1418829278223041</v>
       </c>
       <c r="M22" t="n">
-        <v>7.115556442400473</v>
+        <v>7.101066854610921</v>
       </c>
       <c r="N22" t="n">
-        <v>81.2403763706567</v>
+        <v>81.018979458255</v>
       </c>
       <c r="O22" t="n">
-        <v>9.013344349943406</v>
+        <v>9.001054352588646</v>
       </c>
       <c r="P22" t="n">
-        <v>356.8668143372377</v>
+        <v>356.8510923503528</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32295,28 +32383,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3159219907572758</v>
+        <v>-0.3181057098383139</v>
       </c>
       <c r="J23" t="n">
+        <v>340</v>
+      </c>
+      <c r="K23" t="n">
         <v>339</v>
       </c>
-      <c r="K23" t="n">
-        <v>338</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06841326329841191</v>
+        <v>0.06963588685273059</v>
       </c>
       <c r="M23" t="n">
-        <v>6.565782636260519</v>
+        <v>6.559353189450985</v>
       </c>
       <c r="N23" t="n">
-        <v>72.91513199641767</v>
+        <v>72.7437676232276</v>
       </c>
       <c r="O23" t="n">
-        <v>8.539035776738359</v>
+        <v>8.528995698394249</v>
       </c>
       <c r="P23" t="n">
-        <v>350.7455992064857</v>
+        <v>350.7694291863708</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32354,7 +32442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X340"/>
+  <dimension ref="A1:X341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73637,6 +73725,128 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-37.7569963901495,174.8300066322273</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-37.756280935154656,174.8299463904375</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-37.75559866182563,174.82968433855214</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-37.754891745862544,174.82953781724484</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-37.754175454921906,174.8294050169852</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-37.7534707829641,174.82923206194235</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-37.752778916837514,174.8290220770659</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-37.75212309236497,174.82865355016932</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-37.75142390192563,174.82847356714393</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-37.75075435135982,174.82816723381063</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-37.750081875320795,174.82786202106536</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-37.74938866115175,174.82764184331182</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-37.748742960798644,174.8272493049262</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-37.748072075298374,174.82695242631522</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-37.74737958098928,174.82673448551247</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>-37.74669072510326,174.82650257093664</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>-37.74602948263865,174.8261720808658</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>-37.7453729237383,174.82586520375014</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>-37.74469348487879,174.82567293406692</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>-37.74397928600047,174.82563366882562</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>-37.74329869443801,174.8253348967626</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>-37.74258595590603,174.82525706428675</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X341"/>
+  <dimension ref="A1:X343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26973,6 +26973,162 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="C342" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="D342" t="n">
+        <v>340.18</v>
+      </c>
+      <c r="E342" t="n">
+        <v>343.12</v>
+      </c>
+      <c r="F342" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="G342" t="n">
+        <v>330.21</v>
+      </c>
+      <c r="H342" t="n">
+        <v>328.97</v>
+      </c>
+      <c r="I342" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="J342" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="K342" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="L342" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="M342" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="N342" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="O342" t="n">
+        <v>344.43</v>
+      </c>
+      <c r="P342" t="n">
+        <v>343.21</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="R342" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="S342" t="n">
+        <v>342.82</v>
+      </c>
+      <c r="T342" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="U342" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="V342" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="W342" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="C343" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="D343" t="n">
+        <v>340.18</v>
+      </c>
+      <c r="E343" t="n">
+        <v>340.19</v>
+      </c>
+      <c r="F343" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="G343" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="H343" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="I343" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="J343" t="n">
+        <v>327.59</v>
+      </c>
+      <c r="K343" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="L343" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="M343" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="N343" t="n">
+        <v>346.27</v>
+      </c>
+      <c r="O343" t="n">
+        <v>345.3</v>
+      </c>
+      <c r="P343" t="n">
+        <v>346.42</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>341.71</v>
+      </c>
+      <c r="R343" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="S343" t="n">
+        <v>344.43</v>
+      </c>
+      <c r="T343" t="n">
+        <v>344.78</v>
+      </c>
+      <c r="U343" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="V343" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="W343" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26984,7 +27140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30577,6 +30733,26 @@
       </c>
       <c r="B359" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -30745,28 +30921,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4319682787625641</v>
+        <v>-0.4207889972153601</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1028779438570473</v>
+        <v>0.09860465050785183</v>
       </c>
       <c r="M2" t="n">
-        <v>7.182145692397158</v>
+        <v>7.200152449433196</v>
       </c>
       <c r="N2" t="n">
-        <v>87.43168176038991</v>
+        <v>87.48523209948229</v>
       </c>
       <c r="O2" t="n">
-        <v>9.350490990337882</v>
+        <v>9.353354056138487</v>
       </c>
       <c r="P2" t="n">
-        <v>340.2671987547194</v>
+        <v>340.1440573765426</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30823,28 +30999,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3710931298677224</v>
+        <v>-0.3563136833106596</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03509240119541401</v>
+        <v>0.03265957368658801</v>
       </c>
       <c r="M3" t="n">
-        <v>10.39513027749891</v>
+        <v>10.42390877849009</v>
       </c>
       <c r="N3" t="n">
-        <v>203.7377434821077</v>
+        <v>203.5374055959431</v>
       </c>
       <c r="O3" t="n">
-        <v>14.27367309006717</v>
+        <v>14.26665362290481</v>
       </c>
       <c r="P3" t="n">
-        <v>330.0666856474598</v>
+        <v>329.9043514033573</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30901,28 +31077,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2367799317650955</v>
+        <v>-0.2265553282126231</v>
       </c>
       <c r="J4" t="n">
+        <v>342</v>
+      </c>
+      <c r="K4" t="n">
         <v>340</v>
       </c>
-      <c r="K4" t="n">
-        <v>338</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.009973482805091693</v>
+        <v>0.009231338514335774</v>
       </c>
       <c r="M4" t="n">
-        <v>12.45030894737256</v>
+        <v>12.41495769762386</v>
       </c>
       <c r="N4" t="n">
-        <v>299.087218287976</v>
+        <v>297.8036899325917</v>
       </c>
       <c r="O4" t="n">
-        <v>17.29413826381575</v>
+        <v>17.25698959646762</v>
       </c>
       <c r="P4" t="n">
-        <v>337.3953775229668</v>
+        <v>337.2828760111274</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30979,28 +31155,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6162558007247384</v>
+        <v>-0.5943470336820956</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07812430666191605</v>
+        <v>0.07325460966348618</v>
       </c>
       <c r="M5" t="n">
-        <v>11.84543748732206</v>
+        <v>11.87383646355883</v>
       </c>
       <c r="N5" t="n">
-        <v>242.3523316011479</v>
+        <v>243.1235423378686</v>
       </c>
       <c r="O5" t="n">
-        <v>15.56766943383459</v>
+        <v>15.59241938692866</v>
       </c>
       <c r="P5" t="n">
-        <v>338.6006439478222</v>
+        <v>338.3607675690844</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31057,28 +31233,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8352421026312766</v>
+        <v>-0.8033239454257103</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1127772190203578</v>
+        <v>0.1048594433392123</v>
       </c>
       <c r="M6" t="n">
-        <v>13.19878811079678</v>
+        <v>13.25605195913585</v>
       </c>
       <c r="N6" t="n">
-        <v>293.2684860110779</v>
+        <v>296.1219375882194</v>
       </c>
       <c r="O6" t="n">
-        <v>17.12508353296643</v>
+        <v>17.20819390837456</v>
       </c>
       <c r="P6" t="n">
-        <v>332.3655668750558</v>
+        <v>332.0128806195261</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31135,28 +31311,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03973286542552415</v>
+        <v>0.05798464537594165</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000441874403706688</v>
+        <v>0.0009442282394908075</v>
       </c>
       <c r="M7" t="n">
-        <v>11.04475844757562</v>
+        <v>11.06322207821637</v>
       </c>
       <c r="N7" t="n">
-        <v>194.8058176464477</v>
+        <v>195.2060363634045</v>
       </c>
       <c r="O7" t="n">
-        <v>13.95728546840136</v>
+        <v>13.97161538131524</v>
       </c>
       <c r="P7" t="n">
-        <v>312.6110363625081</v>
+        <v>312.412372886663</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31213,28 +31389,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4431681150952076</v>
+        <v>-0.424043118035654</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03616185898098523</v>
+        <v>0.03339475978856055</v>
       </c>
       <c r="M8" t="n">
-        <v>12.96809194662269</v>
+        <v>12.97511878621362</v>
       </c>
       <c r="N8" t="n">
-        <v>285.6536495918791</v>
+        <v>285.6898723354657</v>
       </c>
       <c r="O8" t="n">
-        <v>16.90129135870627</v>
+        <v>16.90236292165878</v>
       </c>
       <c r="P8" t="n">
-        <v>322.0024609146377</v>
+        <v>321.7942860792866</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31291,28 +31467,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3094422508627097</v>
+        <v>-0.3008886103158078</v>
       </c>
       <c r="J9" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03091156291554775</v>
+        <v>0.029552486286471</v>
       </c>
       <c r="M9" t="n">
-        <v>9.739913182873945</v>
+        <v>9.714301211156668</v>
       </c>
       <c r="N9" t="n">
-        <v>161.523119382231</v>
+        <v>160.9162603162396</v>
       </c>
       <c r="O9" t="n">
-        <v>12.70917461451494</v>
+        <v>12.68527730545295</v>
       </c>
       <c r="P9" t="n">
-        <v>326.9792062579968</v>
+        <v>326.8852618087075</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31369,28 +31545,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4480766386951652</v>
+        <v>-0.4285034054284216</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04447151246181225</v>
+        <v>0.04099075445799061</v>
       </c>
       <c r="M10" t="n">
-        <v>12.98820254336426</v>
+        <v>13.00044457021961</v>
       </c>
       <c r="N10" t="n">
-        <v>232.9936764949317</v>
+        <v>233.371939829656</v>
       </c>
       <c r="O10" t="n">
-        <v>15.26413038777289</v>
+        <v>15.27651595847875</v>
       </c>
       <c r="P10" t="n">
-        <v>322.7967480008135</v>
+        <v>322.5815206359022</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31447,28 +31623,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2953895192956951</v>
+        <v>-0.2786397801699385</v>
       </c>
       <c r="J11" t="n">
+        <v>342</v>
+      </c>
+      <c r="K11" t="n">
         <v>340</v>
       </c>
-      <c r="K11" t="n">
-        <v>338</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02682131318830927</v>
+        <v>0.0240366220933641</v>
       </c>
       <c r="M11" t="n">
-        <v>10.87497357035177</v>
+        <v>10.88160713536285</v>
       </c>
       <c r="N11" t="n">
-        <v>170.3092977113508</v>
+        <v>170.5870110663942</v>
       </c>
       <c r="O11" t="n">
-        <v>13.05026044611182</v>
+        <v>13.0608962581591</v>
       </c>
       <c r="P11" t="n">
-        <v>322.9964254665178</v>
+        <v>322.8122426411236</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31525,28 +31701,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4721308332919808</v>
+        <v>-0.4650670688390896</v>
       </c>
       <c r="J12" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K12" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1464239800810682</v>
+        <v>0.143732618907374</v>
       </c>
       <c r="M12" t="n">
-        <v>6.875088820447857</v>
+        <v>6.866629289592797</v>
       </c>
       <c r="N12" t="n">
-        <v>69.91779894280347</v>
+        <v>69.74220034097753</v>
       </c>
       <c r="O12" t="n">
-        <v>8.361686369555095</v>
+        <v>8.351179577818785</v>
       </c>
       <c r="P12" t="n">
-        <v>337.7508555173773</v>
+        <v>337.673275519677</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31603,28 +31779,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5761313416815367</v>
+        <v>-0.5582072425374506</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K13" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05829103369593736</v>
+        <v>0.05527225519478485</v>
       </c>
       <c r="M13" t="n">
-        <v>13.58672266528024</v>
+        <v>13.56483454970035</v>
       </c>
       <c r="N13" t="n">
-        <v>290.7258124636895</v>
+        <v>290.4561897643957</v>
       </c>
       <c r="O13" t="n">
-        <v>17.05068363625604</v>
+        <v>17.04277529525035</v>
       </c>
       <c r="P13" t="n">
-        <v>340.5066824347194</v>
+        <v>340.3103400801774</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31681,28 +31857,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4701301087488947</v>
+        <v>-0.4508433049658097</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K14" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05246364435646333</v>
+        <v>0.0486287767610154</v>
       </c>
       <c r="M14" t="n">
-        <v>11.65053277981733</v>
+        <v>11.66376107724451</v>
       </c>
       <c r="N14" t="n">
-        <v>214.1045861563703</v>
+        <v>214.5299342848027</v>
       </c>
       <c r="O14" t="n">
-        <v>14.63231308291243</v>
+        <v>14.64684041985857</v>
       </c>
       <c r="P14" t="n">
-        <v>341.2306827806537</v>
+        <v>341.0175739761714</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31759,28 +31935,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3478236417960364</v>
+        <v>-0.3372219081066872</v>
       </c>
       <c r="J15" t="n">
+        <v>342</v>
+      </c>
+      <c r="K15" t="n">
         <v>340</v>
       </c>
-      <c r="K15" t="n">
-        <v>338</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05883546497441716</v>
+        <v>0.05585998158910321</v>
       </c>
       <c r="M15" t="n">
-        <v>7.30233394553191</v>
+        <v>7.299091478739104</v>
       </c>
       <c r="N15" t="n">
-        <v>104.1070647371242</v>
+        <v>104.0080171457494</v>
       </c>
       <c r="O15" t="n">
-        <v>10.2032869575017</v>
+        <v>10.19843209252037</v>
       </c>
       <c r="P15" t="n">
-        <v>344.6949618203203</v>
+        <v>344.5783791977202</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31837,28 +32013,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8787390352533574</v>
+        <v>-0.8607882829464758</v>
       </c>
       <c r="J16" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K16" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1854463378789706</v>
+        <v>0.1798275562964139</v>
       </c>
       <c r="M16" t="n">
-        <v>10.86756416962147</v>
+        <v>10.87970843119949</v>
       </c>
       <c r="N16" t="n">
-        <v>182.3421638825824</v>
+        <v>182.7505243544439</v>
       </c>
       <c r="O16" t="n">
-        <v>13.50341304569265</v>
+        <v>13.51852522853155</v>
       </c>
       <c r="P16" t="n">
-        <v>352.2554180682096</v>
+        <v>352.0577423314047</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31915,28 +32091,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5200002214402277</v>
+        <v>-0.5132535269434494</v>
       </c>
       <c r="J17" t="n">
+        <v>342</v>
+      </c>
+      <c r="K17" t="n">
         <v>340</v>
       </c>
-      <c r="K17" t="n">
-        <v>338</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1218384305016427</v>
+        <v>0.12006554658868</v>
       </c>
       <c r="M17" t="n">
-        <v>7.963942270654935</v>
+        <v>7.950527866659</v>
       </c>
       <c r="N17" t="n">
-        <v>105.0980506666897</v>
+        <v>104.7264113934448</v>
       </c>
       <c r="O17" t="n">
-        <v>10.25173403218644</v>
+        <v>10.23359230150609</v>
       </c>
       <c r="P17" t="n">
-        <v>346.975221593641</v>
+        <v>346.9011418976243</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31993,28 +32169,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6124354491850876</v>
+        <v>-0.6013541174561915</v>
       </c>
       <c r="J18" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K18" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1401101742772924</v>
+        <v>0.1366240380049019</v>
       </c>
       <c r="M18" t="n">
-        <v>8.815244794825372</v>
+        <v>8.805427804042818</v>
       </c>
       <c r="N18" t="n">
-        <v>123.8587809118416</v>
+        <v>123.6926290914896</v>
       </c>
       <c r="O18" t="n">
-        <v>11.12918599502415</v>
+        <v>11.12171880113364</v>
       </c>
       <c r="P18" t="n">
-        <v>350.7439485351377</v>
+        <v>350.6222307924839</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32071,28 +32247,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2119461473880393</v>
+        <v>-0.2059571376120882</v>
       </c>
       <c r="J19" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K19" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02458422360987966</v>
+        <v>0.02347599425128633</v>
       </c>
       <c r="M19" t="n">
-        <v>7.604594964134698</v>
+        <v>7.583213084847461</v>
       </c>
       <c r="N19" t="n">
-        <v>95.89972328627427</v>
+        <v>95.5043231539649</v>
       </c>
       <c r="O19" t="n">
-        <v>9.792840409517265</v>
+        <v>9.772631332142071</v>
       </c>
       <c r="P19" t="n">
-        <v>343.9335161816697</v>
+        <v>343.8677292288908</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32149,28 +32325,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2673803766102785</v>
+        <v>-0.26429346501727</v>
       </c>
       <c r="J20" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K20" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03247963369488871</v>
+        <v>0.03210893162006001</v>
       </c>
       <c r="M20" t="n">
-        <v>8.694811210157514</v>
+        <v>8.658727988625362</v>
       </c>
       <c r="N20" t="n">
-        <v>114.5885112260953</v>
+        <v>113.9682509801997</v>
       </c>
       <c r="O20" t="n">
-        <v>10.70460233853156</v>
+        <v>10.67559136442566</v>
       </c>
       <c r="P20" t="n">
-        <v>347.9480108000439</v>
+        <v>347.9140974034455</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32227,28 +32403,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1885019831661827</v>
+        <v>0.1889852112655812</v>
       </c>
       <c r="J21" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K21" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01697214482812803</v>
+        <v>0.01725064163882373</v>
       </c>
       <c r="M21" t="n">
-        <v>7.654632617235983</v>
+        <v>7.625474476228234</v>
       </c>
       <c r="N21" t="n">
-        <v>110.7373088366337</v>
+        <v>110.1294736107208</v>
       </c>
       <c r="O21" t="n">
-        <v>10.52317959728112</v>
+        <v>10.49425907869254</v>
       </c>
       <c r="P21" t="n">
-        <v>334.6136346802463</v>
+        <v>334.6083107296544</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32305,28 +32481,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4992650210945796</v>
+        <v>-0.4912513826931622</v>
       </c>
       <c r="J22" t="n">
+        <v>342</v>
+      </c>
+      <c r="K22" t="n">
         <v>340</v>
       </c>
-      <c r="K22" t="n">
-        <v>338</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1418829278223041</v>
+        <v>0.1389535506872476</v>
       </c>
       <c r="M22" t="n">
-        <v>7.101066854610921</v>
+        <v>7.095109977333743</v>
       </c>
       <c r="N22" t="n">
-        <v>81.018979458255</v>
+        <v>80.84225741558002</v>
       </c>
       <c r="O22" t="n">
-        <v>9.001054352588646</v>
+        <v>8.991232252343393</v>
       </c>
       <c r="P22" t="n">
-        <v>356.8510923503528</v>
+        <v>356.7629110353753</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32383,28 +32559,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3181057098383139</v>
+        <v>-0.3140586808112421</v>
       </c>
       <c r="J23" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K23" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06963588685273059</v>
+        <v>0.06866228585774425</v>
       </c>
       <c r="M23" t="n">
-        <v>6.559353189450985</v>
+        <v>6.53888880863003</v>
       </c>
       <c r="N23" t="n">
-        <v>72.7437676232276</v>
+        <v>72.41373417216775</v>
       </c>
       <c r="O23" t="n">
-        <v>8.528995698394249</v>
+        <v>8.509625971343732</v>
       </c>
       <c r="P23" t="n">
-        <v>350.7694291863708</v>
+        <v>350.7249654851277</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32442,7 +32618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X341"/>
+  <dimension ref="A1:X343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73847,6 +74023,250 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-37.75700189107543,174.8299731821419</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-37.75629487932776,174.82986159916078</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-37.75561015696039,174.82961443913848</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-37.75491523631202,174.82940989113348</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-37.75420994823383,174.82924536178874</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-37.75350134337929,174.8290987155946</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-37.75281309094347,174.82887374590828</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-37.75212415921417,174.82864897726503</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-37.751443821878176,174.8283888006255</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-37.750763571019284,174.82812830294657</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-37.75008351857018,174.82785541549597</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-37.74942785811165,174.82749048116725</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-37.748760477743566,174.82718166178293</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-37.748079791419435,174.82692289166195</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-37.74739861575838,174.8266632931155</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-37.746703800878045,174.82645435597507</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>-37.746050013474886,174.82609637644586</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>-37.74538035885587,174.8258308261137</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>-37.74469408899922,174.82566892061192</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>-37.74398656449214,174.82558205365106</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>-37.74330435760471,174.82529721346933</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>-37.74259543818904,174.8251965042704</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-37.75700189107543,174.8299731821419</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-37.75629487932776,174.82986159916078</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-37.75561015696039,174.82961443913848</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-37.75490928757673,174.82944228729602</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-37.75420786633901,174.82925499804645</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-37.75350044381073,174.82910264075448</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-37.75280513123054,174.8289082947653</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-37.75211852015207,174.82867314832902</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-37.75144042091491,174.82840327296128</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-37.7507616137742,174.82813656760013</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-37.75007751127967,174.8278795637236</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-37.749425036383904,174.8275013775211</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-37.74876321563583,174.82717108916742</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-37.748082241427156,174.82691351386924</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-37.74740784559348,174.82662877231715</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-37.7467187113148,174.8263993758637</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>-37.74605260530758,174.82608681943088</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>-37.74538417112569,174.825813199361</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>-37.7446980996842,174.82564227572848</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>-37.7439948512325,174.825523288309</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>-37.74330817772227,174.8252717939662</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>-37.742602201269165,174.82515331071912</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X343"/>
+  <dimension ref="A1:X345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27129,6 +27129,162 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="C344" t="n">
+        <v>334.35</v>
+      </c>
+      <c r="D344" t="n">
+        <v>342.04</v>
+      </c>
+      <c r="E344" t="n">
+        <v>340.84</v>
+      </c>
+      <c r="F344" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="G344" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="H344" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="I344" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="J344" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="K344" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="L344" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="M344" t="n">
+        <v>340.28</v>
+      </c>
+      <c r="N344" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="O344" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="P344" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="R344" t="n">
+        <v>345.82</v>
+      </c>
+      <c r="S344" t="n">
+        <v>345.31</v>
+      </c>
+      <c r="T344" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="U344" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="V344" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="W344" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>341.36</v>
+      </c>
+      <c r="C345" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="D345" t="n">
+        <v>343.98</v>
+      </c>
+      <c r="E345" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="F345" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="G345" t="n">
+        <v>328.53</v>
+      </c>
+      <c r="H345" t="n">
+        <v>323.4</v>
+      </c>
+      <c r="I345" t="n">
+        <v>325.29</v>
+      </c>
+      <c r="J345" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="K345" t="n">
+        <v>327.79</v>
+      </c>
+      <c r="L345" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="M345" t="n">
+        <v>339.88</v>
+      </c>
+      <c r="N345" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="O345" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="P345" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="R345" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="S345" t="n">
+        <v>347.13</v>
+      </c>
+      <c r="T345" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="U345" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="V345" t="n">
+        <v>354.39</v>
+      </c>
+      <c r="W345" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27140,7 +27296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30753,6 +30909,26 @@
       </c>
       <c r="B361" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -30921,28 +31097,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4207889972153601</v>
+        <v>-0.4073931429643239</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09860465050785183</v>
+        <v>0.09318557819395945</v>
       </c>
       <c r="M2" t="n">
-        <v>7.200152449433196</v>
+        <v>7.230534324267436</v>
       </c>
       <c r="N2" t="n">
-        <v>87.48523209948229</v>
+        <v>87.80270808193416</v>
       </c>
       <c r="O2" t="n">
-        <v>9.353354056138487</v>
+        <v>9.370309924540072</v>
       </c>
       <c r="P2" t="n">
-        <v>340.1440573765426</v>
+        <v>339.9959787330666</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30999,28 +31175,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3563136833106596</v>
+        <v>-0.3402895828811496</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03265957368658801</v>
+        <v>0.0300442476657885</v>
       </c>
       <c r="M3" t="n">
-        <v>10.42390877849009</v>
+        <v>10.4607692071649</v>
       </c>
       <c r="N3" t="n">
-        <v>203.5374055959431</v>
+        <v>203.5381284184201</v>
       </c>
       <c r="O3" t="n">
-        <v>14.26665362290481</v>
+        <v>14.26667895546893</v>
       </c>
       <c r="P3" t="n">
-        <v>329.9043514033573</v>
+        <v>329.7277282242228</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31077,28 +31253,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2265553282126231</v>
+        <v>-0.2134301131883908</v>
       </c>
       <c r="J4" t="n">
+        <v>344</v>
+      </c>
+      <c r="K4" t="n">
         <v>342</v>
       </c>
-      <c r="K4" t="n">
-        <v>340</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.009231338514335774</v>
+        <v>0.008274783964331012</v>
       </c>
       <c r="M4" t="n">
-        <v>12.41495769762386</v>
+        <v>12.39035220153218</v>
       </c>
       <c r="N4" t="n">
-        <v>297.8036899325917</v>
+        <v>296.8630318034282</v>
       </c>
       <c r="O4" t="n">
-        <v>17.25698959646762</v>
+        <v>17.22971363091761</v>
       </c>
       <c r="P4" t="n">
-        <v>337.2828760111274</v>
+        <v>337.1379435663824</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31155,28 +31331,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5943470336820956</v>
+        <v>-0.5734792861129112</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07325460966348618</v>
+        <v>0.06876816547119891</v>
       </c>
       <c r="M5" t="n">
-        <v>11.87383646355883</v>
+        <v>11.89790897891643</v>
       </c>
       <c r="N5" t="n">
-        <v>243.1235423378686</v>
+        <v>243.7131384603891</v>
       </c>
       <c r="O5" t="n">
-        <v>15.59241938692866</v>
+        <v>15.61131443730441</v>
       </c>
       <c r="P5" t="n">
-        <v>338.3607675690844</v>
+        <v>338.1314765984336</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31233,28 +31409,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8033239454257103</v>
+        <v>-0.7739963292874192</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1048594433392123</v>
+        <v>0.09794713778470521</v>
       </c>
       <c r="M6" t="n">
-        <v>13.25605195913585</v>
+        <v>13.30127007083798</v>
       </c>
       <c r="N6" t="n">
-        <v>296.1219375882194</v>
+        <v>298.3111368079028</v>
       </c>
       <c r="O6" t="n">
-        <v>17.20819390837456</v>
+        <v>17.27168598625805</v>
       </c>
       <c r="P6" t="n">
-        <v>332.0128806195261</v>
+        <v>331.6876865265057</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31311,28 +31487,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05798464537594165</v>
+        <v>0.07448284975266699</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009442282394908075</v>
+        <v>0.001564984095939859</v>
       </c>
       <c r="M7" t="n">
-        <v>11.06322207821637</v>
+        <v>11.07351867999797</v>
       </c>
       <c r="N7" t="n">
-        <v>195.2060363634045</v>
+        <v>195.3477840850595</v>
       </c>
       <c r="O7" t="n">
-        <v>13.97161538131524</v>
+        <v>13.97668716416947</v>
       </c>
       <c r="P7" t="n">
-        <v>312.412372886663</v>
+        <v>312.2321674197385</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31389,28 +31565,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.424043118035654</v>
+        <v>-0.4089713322809616</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03339475978856055</v>
+        <v>0.03137459301912815</v>
       </c>
       <c r="M8" t="n">
-        <v>12.97511878621362</v>
+        <v>12.96538534870495</v>
       </c>
       <c r="N8" t="n">
-        <v>285.6898723354657</v>
+        <v>285.0967389209921</v>
       </c>
       <c r="O8" t="n">
-        <v>16.90236292165878</v>
+        <v>16.88480793260593</v>
       </c>
       <c r="P8" t="n">
-        <v>321.7942860792866</v>
+        <v>321.6296531180679</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31467,28 +31643,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3008886103158078</v>
+        <v>-0.2936429919461475</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.029552486286471</v>
+        <v>0.02846665964906137</v>
       </c>
       <c r="M9" t="n">
-        <v>9.714301211156668</v>
+        <v>9.684107083647262</v>
       </c>
       <c r="N9" t="n">
-        <v>160.9162603162396</v>
+        <v>160.2206020326672</v>
       </c>
       <c r="O9" t="n">
-        <v>12.68527730545295</v>
+        <v>12.65782769801624</v>
       </c>
       <c r="P9" t="n">
-        <v>326.8852618087075</v>
+        <v>326.8054014878401</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31545,28 +31721,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4285034054284216</v>
+        <v>-0.4101890264749611</v>
       </c>
       <c r="J10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04099075445799061</v>
+        <v>0.03787100037069691</v>
       </c>
       <c r="M10" t="n">
-        <v>13.00044457021961</v>
+        <v>13.00623449668371</v>
       </c>
       <c r="N10" t="n">
-        <v>233.371939829656</v>
+        <v>233.5575160927602</v>
       </c>
       <c r="O10" t="n">
-        <v>15.27651595847875</v>
+        <v>15.2825886581024</v>
       </c>
       <c r="P10" t="n">
-        <v>322.5815206359022</v>
+        <v>322.3794233746634</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31623,28 +31799,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2786397801699385</v>
+        <v>-0.2637510027014016</v>
       </c>
       <c r="J11" t="n">
+        <v>344</v>
+      </c>
+      <c r="K11" t="n">
         <v>342</v>
       </c>
-      <c r="K11" t="n">
-        <v>340</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0240366220933641</v>
+        <v>0.02170997115742146</v>
       </c>
       <c r="M11" t="n">
-        <v>10.88160713536285</v>
+        <v>10.88094580465669</v>
       </c>
       <c r="N11" t="n">
-        <v>170.5870110663942</v>
+        <v>170.6202328335242</v>
       </c>
       <c r="O11" t="n">
-        <v>13.0608962581591</v>
+        <v>13.06216799897797</v>
       </c>
       <c r="P11" t="n">
-        <v>322.8122426411236</v>
+        <v>322.6479615736718</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31701,28 +31877,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4650670688390896</v>
+        <v>-0.4588232708648656</v>
       </c>
       <c r="J12" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K12" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
-        <v>0.143732618907374</v>
+        <v>0.1415415333082449</v>
       </c>
       <c r="M12" t="n">
-        <v>6.866629289592797</v>
+        <v>6.854641943874614</v>
       </c>
       <c r="N12" t="n">
-        <v>69.74220034097753</v>
+        <v>69.51589902905263</v>
       </c>
       <c r="O12" t="n">
-        <v>8.351179577818785</v>
+        <v>8.337619506133189</v>
       </c>
       <c r="P12" t="n">
-        <v>337.673275519677</v>
+        <v>337.6044538700735</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31779,28 +31955,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5582072425374506</v>
+        <v>-0.5417646853207631</v>
       </c>
       <c r="J13" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K13" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05527225519478485</v>
+        <v>0.05260222624815125</v>
       </c>
       <c r="M13" t="n">
-        <v>13.56483454970035</v>
+        <v>13.5389333289263</v>
       </c>
       <c r="N13" t="n">
-        <v>290.4561897643957</v>
+        <v>289.9836028192055</v>
       </c>
       <c r="O13" t="n">
-        <v>17.04277529525035</v>
+        <v>17.02890492131557</v>
       </c>
       <c r="P13" t="n">
-        <v>340.3103400801774</v>
+        <v>340.1295905136184</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31857,28 +32033,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4508433049658097</v>
+        <v>-0.4331528453045356</v>
       </c>
       <c r="J14" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K14" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0486287767610154</v>
+        <v>0.0452670758044682</v>
       </c>
       <c r="M14" t="n">
-        <v>11.66376107724451</v>
+        <v>11.66973768930067</v>
       </c>
       <c r="N14" t="n">
-        <v>214.5299342848027</v>
+        <v>214.7139186844268</v>
       </c>
       <c r="O14" t="n">
-        <v>14.64684041985857</v>
+        <v>14.65311975943781</v>
       </c>
       <c r="P14" t="n">
-        <v>341.0175739761714</v>
+        <v>340.821428700451</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31935,28 +32111,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3372219081066872</v>
+        <v>-0.3265237198278232</v>
       </c>
       <c r="J15" t="n">
+        <v>344</v>
+      </c>
+      <c r="K15" t="n">
         <v>342</v>
       </c>
-      <c r="K15" t="n">
-        <v>340</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05585998158910321</v>
+        <v>0.05288417769288389</v>
       </c>
       <c r="M15" t="n">
-        <v>7.299091478739104</v>
+        <v>7.296971532923068</v>
       </c>
       <c r="N15" t="n">
-        <v>104.0080171457494</v>
+        <v>103.9299499029091</v>
       </c>
       <c r="O15" t="n">
-        <v>10.19843209252037</v>
+        <v>10.19460396008148</v>
       </c>
       <c r="P15" t="n">
-        <v>344.5783791977202</v>
+        <v>344.4603326551209</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32013,28 +32189,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8607882829464758</v>
+        <v>-0.8415417254273138</v>
       </c>
       <c r="J16" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K16" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1798275562964139</v>
+        <v>0.1735809817522894</v>
       </c>
       <c r="M16" t="n">
-        <v>10.87970843119949</v>
+        <v>10.89657698566112</v>
       </c>
       <c r="N16" t="n">
-        <v>182.7505243544439</v>
+        <v>183.3952700632784</v>
       </c>
       <c r="O16" t="n">
-        <v>13.51852522853155</v>
+        <v>13.54235097991772</v>
       </c>
       <c r="P16" t="n">
-        <v>352.0577423314047</v>
+        <v>351.8450746215632</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32091,28 +32267,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5132535269434494</v>
+        <v>-0.5034107446907202</v>
       </c>
       <c r="J17" t="n">
+        <v>344</v>
+      </c>
+      <c r="K17" t="n">
         <v>342</v>
       </c>
-      <c r="K17" t="n">
-        <v>340</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.12006554658868</v>
+        <v>0.1167925996592405</v>
       </c>
       <c r="M17" t="n">
-        <v>7.950527866659</v>
+        <v>7.952928899674278</v>
       </c>
       <c r="N17" t="n">
-        <v>104.7264113934448</v>
+        <v>104.5648975442529</v>
       </c>
       <c r="O17" t="n">
-        <v>10.23359230150609</v>
+        <v>10.22569790010701</v>
       </c>
       <c r="P17" t="n">
-        <v>346.9011418976243</v>
+        <v>346.7927185821057</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32169,28 +32345,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6013541174561915</v>
+        <v>-0.5889796139247299</v>
       </c>
       <c r="J18" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K18" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1366240380049019</v>
+        <v>0.1324777334292427</v>
       </c>
       <c r="M18" t="n">
-        <v>8.805427804042818</v>
+        <v>8.800395264183065</v>
       </c>
       <c r="N18" t="n">
-        <v>123.6926290914896</v>
+        <v>123.6790514341541</v>
       </c>
       <c r="O18" t="n">
-        <v>11.12171880113364</v>
+        <v>11.12110837255685</v>
       </c>
       <c r="P18" t="n">
-        <v>350.6222307924839</v>
+        <v>350.4858402531769</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32247,28 +32423,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2059571376120882</v>
+        <v>-0.1972210375309911</v>
       </c>
       <c r="J19" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K19" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02347599425128633</v>
+        <v>0.02173726471034443</v>
       </c>
       <c r="M19" t="n">
-        <v>7.583213084847461</v>
+        <v>7.57238739656963</v>
       </c>
       <c r="N19" t="n">
-        <v>95.5043231539649</v>
+        <v>95.3048435740687</v>
       </c>
       <c r="O19" t="n">
-        <v>9.772631332142071</v>
+        <v>9.762419965053168</v>
       </c>
       <c r="P19" t="n">
-        <v>343.8677292288908</v>
+        <v>343.7714286653679</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32325,28 +32501,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.26429346501727</v>
+        <v>-0.2562146194542912</v>
       </c>
       <c r="J20" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K20" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03210893162006001</v>
+        <v>0.03049938948165554</v>
       </c>
       <c r="M20" t="n">
-        <v>8.658727988625362</v>
+        <v>8.646986395755874</v>
       </c>
       <c r="N20" t="n">
-        <v>113.9682509801997</v>
+        <v>113.6115886154763</v>
       </c>
       <c r="O20" t="n">
-        <v>10.67559136442566</v>
+        <v>10.65887370295175</v>
       </c>
       <c r="P20" t="n">
-        <v>347.9140974034455</v>
+        <v>347.8250394348109</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32403,28 +32579,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1889852112655812</v>
+        <v>0.1941006232014608</v>
       </c>
       <c r="J21" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K21" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01725064163882373</v>
+        <v>0.01837003905670276</v>
       </c>
       <c r="M21" t="n">
-        <v>7.625474476228234</v>
+        <v>7.610539886089006</v>
       </c>
       <c r="N21" t="n">
-        <v>110.1294736107208</v>
+        <v>109.6098197212808</v>
       </c>
       <c r="O21" t="n">
-        <v>10.49425907869254</v>
+        <v>10.46947084246768</v>
       </c>
       <c r="P21" t="n">
-        <v>334.6083107296544</v>
+        <v>334.5519221398345</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32481,28 +32657,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4912513826931622</v>
+        <v>-0.4796034610666342</v>
       </c>
       <c r="J22" t="n">
+        <v>344</v>
+      </c>
+      <c r="K22" t="n">
         <v>342</v>
       </c>
-      <c r="K22" t="n">
-        <v>340</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1389535506872476</v>
+        <v>0.1337653751027318</v>
       </c>
       <c r="M22" t="n">
-        <v>7.095109977333743</v>
+        <v>7.105146110932597</v>
       </c>
       <c r="N22" t="n">
-        <v>80.84225741558002</v>
+        <v>80.99654275449869</v>
       </c>
       <c r="O22" t="n">
-        <v>8.991232252343393</v>
+        <v>8.999807928755963</v>
       </c>
       <c r="P22" t="n">
-        <v>356.7629110353753</v>
+        <v>356.6342983186487</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32559,28 +32735,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3140586808112421</v>
+        <v>-0.3071596076822212</v>
       </c>
       <c r="J23" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K23" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06866228585774425</v>
+        <v>0.06641039639262858</v>
       </c>
       <c r="M23" t="n">
-        <v>6.53888880863003</v>
+        <v>6.531233942494501</v>
       </c>
       <c r="N23" t="n">
-        <v>72.41373417216775</v>
+        <v>72.21144257019853</v>
       </c>
       <c r="O23" t="n">
-        <v>8.509625971343732</v>
+        <v>8.497731613212936</v>
       </c>
       <c r="P23" t="n">
-        <v>350.7249654851277</v>
+        <v>350.6489232609003</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32618,7 +32794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X343"/>
+  <dimension ref="A1:X345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74267,6 +74443,250 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-37.75700516238573,174.8299532898959</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-37.756296725144324,174.8298503751491</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-37.75561355614979,174.8295937693551</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-37.7549106072628,174.8294351004345</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-37.75420443594244,174.82927087596988</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-37.753498994505556,174.82910896462295</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-37.752802896482855,174.82891799460074</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-37.752119028175876,174.82867097075584</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-37.75144098348038,174.8284008790412</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-37.750761768293565,174.82813591512752</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-37.7500783733127,174.82787609850735</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-37.74942444968793,174.8275036430995</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-37.74876103649717,174.82717950410637</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-37.74808297361322,174.82691071131035</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-37.74740962830193,174.8266221047476</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-37.74672127404359,174.82638992615475</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>-37.74605569220842,174.82607543691776</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>-37.74538625484973,174.8258035648618</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>-37.74470194255251,174.82561674569078</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>-37.743996458163586,174.82551189274673</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>-37.743311528698115,174.82524949615413</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>-37.74260333425787,174.82514607468522</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-37.75700675235099,174.8299436215969</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-37.756298351655076,174.82984048468288</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-37.75561710153706,174.82957221054664</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-37.75491212997695,174.82942680790163</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-37.75420587907504,174.82926419629194</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-37.75349714539156,174.8291170330065</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-37.75279910494285,174.8289344516235</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-37.75211862175684,174.82867271281438</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-37.75143978163591,174.82840599332502</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-37.75075684942523,174.8281566855049</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-37.75007942391531,174.8278718752749</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-37.74942333217162,174.82750795848685</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-37.748757153158856,174.8271944999578</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-37.74808088969885,174.8269186878239</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-37.74740571784421,174.82663673038363</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-37.74671818712018,174.82640130875865</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>-37.74605502240927,174.82607790670846</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>-37.74539056436742,174.82578363896394</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>-37.744705466575404,174.8255933338633</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>-37.743998143864644,174.8254999385779</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>-37.74331246697061,174.82524325276634</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>-37.74260350856378,174.82514496144918</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X345"/>
+  <dimension ref="A1:X346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27285,6 +27285,84 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="C346" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="D346" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="E346" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="F346" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="G346" t="n">
+        <v>327.55</v>
+      </c>
+      <c r="H346" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="I346" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="J346" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="K346" t="n">
+        <v>326.54</v>
+      </c>
+      <c r="L346" t="n">
+        <v>328.77</v>
+      </c>
+      <c r="M346" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="N346" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="O346" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="P346" t="n">
+        <v>344.47</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>341.73</v>
+      </c>
+      <c r="R346" t="n">
+        <v>344.63</v>
+      </c>
+      <c r="S346" t="n">
+        <v>346.87</v>
+      </c>
+      <c r="T346" t="n">
+        <v>349.36</v>
+      </c>
+      <c r="U346" t="n">
+        <v>343.21</v>
+      </c>
+      <c r="V346" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="W346" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27296,7 +27374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30929,6 +31007,16 @@
       </c>
       <c r="B363" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -31097,28 +31185,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4073931429643239</v>
+        <v>-0.4005877371533592</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09318557819395945</v>
+        <v>0.0904538007750002</v>
       </c>
       <c r="M2" t="n">
-        <v>7.230534324267436</v>
+        <v>7.246005274189969</v>
       </c>
       <c r="N2" t="n">
-        <v>87.80270808193416</v>
+        <v>87.976999737553</v>
       </c>
       <c r="O2" t="n">
-        <v>9.370309924540072</v>
+        <v>9.379605521425354</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9959787330666</v>
+        <v>339.920454009685</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31175,28 +31263,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3402895828811496</v>
+        <v>-0.3318940543357164</v>
       </c>
       <c r="J3" t="n">
+        <v>345</v>
+      </c>
+      <c r="K3" t="n">
         <v>344</v>
       </c>
-      <c r="K3" t="n">
-        <v>343</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0300442476657885</v>
+        <v>0.02869507393565984</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4607692071649</v>
+        <v>10.48107881562698</v>
       </c>
       <c r="N3" t="n">
-        <v>203.5381284184201</v>
+        <v>203.602176870495</v>
       </c>
       <c r="O3" t="n">
-        <v>14.26667895546893</v>
+        <v>14.2689234657172</v>
       </c>
       <c r="P3" t="n">
-        <v>329.7277282242228</v>
+        <v>329.6348253618476</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31253,28 +31341,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2134301131883908</v>
+        <v>-0.2055904156867176</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008274783964331012</v>
+        <v>0.007712572063984235</v>
       </c>
       <c r="M4" t="n">
-        <v>12.39035220153218</v>
+        <v>12.38258353723996</v>
       </c>
       <c r="N4" t="n">
-        <v>296.8630318034282</v>
+        <v>296.5690193201898</v>
       </c>
       <c r="O4" t="n">
-        <v>17.22971363091761</v>
+        <v>17.22117938238232</v>
       </c>
       <c r="P4" t="n">
-        <v>337.1379435663824</v>
+        <v>337.0510382110789</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31331,28 +31419,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5734792861129112</v>
+        <v>-0.5636993023605315</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06876816547119891</v>
+        <v>0.06673525613616615</v>
       </c>
       <c r="M5" t="n">
-        <v>11.89790897891643</v>
+        <v>11.90705942979066</v>
       </c>
       <c r="N5" t="n">
-        <v>243.7131384603891</v>
+        <v>243.8916268694085</v>
       </c>
       <c r="O5" t="n">
-        <v>15.61131443730441</v>
+        <v>15.61703002716613</v>
       </c>
       <c r="P5" t="n">
-        <v>338.1314765984336</v>
+        <v>338.0235893450347</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31409,28 +31497,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7739963292874192</v>
+        <v>-0.7584685855113038</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09794713778470521</v>
+        <v>0.09429109304075489</v>
       </c>
       <c r="M6" t="n">
-        <v>13.30127007083798</v>
+        <v>13.32742955670615</v>
       </c>
       <c r="N6" t="n">
-        <v>298.3111368079028</v>
+        <v>299.6547957987735</v>
       </c>
       <c r="O6" t="n">
-        <v>17.27168598625805</v>
+        <v>17.3105400204261</v>
       </c>
       <c r="P6" t="n">
-        <v>331.6876865265057</v>
+        <v>331.5148293677081</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31487,28 +31575,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07448284975266699</v>
+        <v>0.08183838844092822</v>
       </c>
       <c r="J7" t="n">
+        <v>345</v>
+      </c>
+      <c r="K7" t="n">
         <v>344</v>
       </c>
-      <c r="K7" t="n">
-        <v>343</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001564984095939859</v>
+        <v>0.00189479295343864</v>
       </c>
       <c r="M7" t="n">
-        <v>11.07351867999797</v>
+        <v>11.07498361064214</v>
       </c>
       <c r="N7" t="n">
-        <v>195.3477840850595</v>
+        <v>195.2917924159455</v>
       </c>
       <c r="O7" t="n">
-        <v>13.97668716416947</v>
+        <v>13.97468398268617</v>
       </c>
       <c r="P7" t="n">
-        <v>312.2321674197385</v>
+        <v>312.1514999679822</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31565,28 +31653,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4089713322809616</v>
+        <v>-0.4027656629349165</v>
       </c>
       <c r="J8" t="n">
+        <v>345</v>
+      </c>
+      <c r="K8" t="n">
         <v>344</v>
       </c>
-      <c r="K8" t="n">
-        <v>343</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03137459301912815</v>
+        <v>0.0305928983148922</v>
       </c>
       <c r="M8" t="n">
-        <v>12.96538534870495</v>
+        <v>12.95450887960407</v>
       </c>
       <c r="N8" t="n">
-        <v>285.0967389209921</v>
+        <v>284.6329165079598</v>
       </c>
       <c r="O8" t="n">
-        <v>16.88480793260593</v>
+        <v>16.87106743830869</v>
       </c>
       <c r="P8" t="n">
-        <v>321.6296531180679</v>
+        <v>321.5615905122172</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31643,28 +31731,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2936429919461475</v>
+        <v>-0.291019090979146</v>
       </c>
       <c r="J9" t="n">
+        <v>345</v>
+      </c>
+      <c r="K9" t="n">
         <v>344</v>
       </c>
-      <c r="K9" t="n">
-        <v>343</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02846665964906137</v>
+        <v>0.02812298253786383</v>
       </c>
       <c r="M9" t="n">
-        <v>9.684107083647262</v>
+        <v>9.665465980846319</v>
       </c>
       <c r="N9" t="n">
-        <v>160.2206020326672</v>
+        <v>159.8188950717118</v>
       </c>
       <c r="O9" t="n">
-        <v>12.65782769801624</v>
+        <v>12.64194981289325</v>
       </c>
       <c r="P9" t="n">
-        <v>326.8054014878401</v>
+        <v>326.7763660424712</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31721,28 +31809,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4101890264749611</v>
+        <v>-0.4029151593925033</v>
       </c>
       <c r="J10" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03787100037069691</v>
+        <v>0.03671914610674443</v>
       </c>
       <c r="M10" t="n">
-        <v>13.00623449668371</v>
+        <v>13.00092737511338</v>
       </c>
       <c r="N10" t="n">
-        <v>233.5575160927602</v>
+        <v>233.3665941388373</v>
       </c>
       <c r="O10" t="n">
-        <v>15.2825886581024</v>
+        <v>15.27634099314483</v>
       </c>
       <c r="P10" t="n">
-        <v>322.3794233746634</v>
+        <v>322.2988324967897</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31799,28 +31887,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2637510027014016</v>
+        <v>-0.2576522818173838</v>
       </c>
       <c r="J11" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K11" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02170997115742146</v>
+        <v>0.02081572263067688</v>
       </c>
       <c r="M11" t="n">
-        <v>10.88094580465669</v>
+        <v>10.87470759042915</v>
       </c>
       <c r="N11" t="n">
-        <v>170.6202328335242</v>
+        <v>170.4691028679715</v>
       </c>
       <c r="O11" t="n">
-        <v>13.06216799897797</v>
+        <v>13.05638169126391</v>
       </c>
       <c r="P11" t="n">
-        <v>322.6479615736718</v>
+        <v>322.580396233307</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31877,28 +31965,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4588232708648656</v>
+        <v>-0.4569126335511384</v>
       </c>
       <c r="J12" t="n">
+        <v>345</v>
+      </c>
+      <c r="K12" t="n">
         <v>344</v>
       </c>
-      <c r="K12" t="n">
-        <v>343</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1415415333082449</v>
+        <v>0.1411794348637626</v>
       </c>
       <c r="M12" t="n">
-        <v>6.854641943874614</v>
+        <v>6.843193658358786</v>
       </c>
       <c r="N12" t="n">
-        <v>69.51589902905263</v>
+        <v>69.34777927008257</v>
       </c>
       <c r="O12" t="n">
-        <v>8.337619506133189</v>
+        <v>8.327531403127974</v>
       </c>
       <c r="P12" t="n">
-        <v>337.6044538700735</v>
+        <v>337.5833112255758</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31955,28 +32043,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5417646853207631</v>
+        <v>-0.5356040769204072</v>
       </c>
       <c r="J13" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K13" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05260222624815125</v>
+        <v>0.05170219700009182</v>
       </c>
       <c r="M13" t="n">
-        <v>13.5389333289263</v>
+        <v>13.51916098001008</v>
       </c>
       <c r="N13" t="n">
-        <v>289.9836028192055</v>
+        <v>289.4792721385528</v>
       </c>
       <c r="O13" t="n">
-        <v>17.02890492131557</v>
+        <v>17.01409039997592</v>
       </c>
       <c r="P13" t="n">
-        <v>340.1295905136184</v>
+        <v>340.0615946579476</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32033,28 +32121,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4331528453045356</v>
+        <v>-0.4263319639965599</v>
       </c>
       <c r="J14" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K14" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0452670758044682</v>
+        <v>0.04407505425314218</v>
       </c>
       <c r="M14" t="n">
-        <v>11.66973768930067</v>
+        <v>11.66435844504998</v>
       </c>
       <c r="N14" t="n">
-        <v>214.7139186844268</v>
+        <v>214.5153170850826</v>
       </c>
       <c r="O14" t="n">
-        <v>14.65311975943781</v>
+        <v>14.64634142320472</v>
       </c>
       <c r="P14" t="n">
-        <v>340.821428700451</v>
+        <v>340.7454948784457</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32111,28 +32199,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3265237198278232</v>
+        <v>-0.3219803022045273</v>
       </c>
       <c r="J15" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K15" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05288417769288389</v>
+        <v>0.05169335357342897</v>
       </c>
       <c r="M15" t="n">
-        <v>7.296971532923068</v>
+        <v>7.292976164719271</v>
       </c>
       <c r="N15" t="n">
-        <v>103.9299499029091</v>
+        <v>103.8191441793165</v>
       </c>
       <c r="O15" t="n">
-        <v>10.19460396008148</v>
+        <v>10.18916798268222</v>
       </c>
       <c r="P15" t="n">
-        <v>344.4603326551209</v>
+        <v>344.4099979105121</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32189,28 +32277,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8415417254273138</v>
+        <v>-0.8331026219073825</v>
       </c>
       <c r="J16" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K16" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1735809817522894</v>
+        <v>0.1710227911698439</v>
       </c>
       <c r="M16" t="n">
-        <v>10.89657698566112</v>
+        <v>10.89967358252089</v>
       </c>
       <c r="N16" t="n">
-        <v>183.3952700632784</v>
+        <v>183.52231596398</v>
       </c>
       <c r="O16" t="n">
-        <v>13.54235097991772</v>
+        <v>13.54704085636343</v>
       </c>
       <c r="P16" t="n">
-        <v>351.8450746215632</v>
+        <v>351.7514496519253</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32267,28 +32355,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5034107446907202</v>
+        <v>-0.4987364342474288</v>
       </c>
       <c r="J17" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K17" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1167925996592405</v>
+        <v>0.1152779242905158</v>
       </c>
       <c r="M17" t="n">
-        <v>7.952928899674278</v>
+        <v>7.952947519369636</v>
       </c>
       <c r="N17" t="n">
-        <v>104.5648975442529</v>
+        <v>104.4640191367458</v>
       </c>
       <c r="O17" t="n">
-        <v>10.22569790010701</v>
+        <v>10.22076411706805</v>
       </c>
       <c r="P17" t="n">
-        <v>346.7927185821057</v>
+        <v>346.7410202076528</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32345,28 +32433,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5889796139247299</v>
+        <v>-0.5834739871942866</v>
       </c>
       <c r="J18" t="n">
+        <v>345</v>
+      </c>
+      <c r="K18" t="n">
         <v>344</v>
       </c>
-      <c r="K18" t="n">
-        <v>343</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1324777334292427</v>
+        <v>0.1307388614308741</v>
       </c>
       <c r="M18" t="n">
-        <v>8.800395264183065</v>
+        <v>8.795853186652755</v>
       </c>
       <c r="N18" t="n">
-        <v>123.6790514341541</v>
+        <v>123.6015146090878</v>
       </c>
       <c r="O18" t="n">
-        <v>11.12110837255685</v>
+        <v>11.11762180545317</v>
       </c>
       <c r="P18" t="n">
-        <v>350.4858402531769</v>
+        <v>350.4249163363968</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32423,28 +32511,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1972210375309911</v>
+        <v>-0.1925605397132484</v>
       </c>
       <c r="J19" t="n">
+        <v>345</v>
+      </c>
+      <c r="K19" t="n">
         <v>344</v>
       </c>
-      <c r="K19" t="n">
-        <v>343</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02173726471034443</v>
+        <v>0.02081898980227059</v>
       </c>
       <c r="M19" t="n">
-        <v>7.57238739656963</v>
+        <v>7.567971767319383</v>
       </c>
       <c r="N19" t="n">
-        <v>95.3048435740687</v>
+        <v>95.22986047881508</v>
       </c>
       <c r="O19" t="n">
-        <v>9.762419965053168</v>
+        <v>9.758578814500352</v>
       </c>
       <c r="P19" t="n">
-        <v>343.7714286653679</v>
+        <v>343.7198567381189</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32501,28 +32589,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2562146194542912</v>
+        <v>-0.2515474019427948</v>
       </c>
       <c r="J20" t="n">
+        <v>345</v>
+      </c>
+      <c r="K20" t="n">
         <v>344</v>
       </c>
-      <c r="K20" t="n">
-        <v>343</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.03049938948165554</v>
+        <v>0.02954709842407022</v>
       </c>
       <c r="M20" t="n">
-        <v>8.646986395755874</v>
+        <v>8.644125832073817</v>
       </c>
       <c r="N20" t="n">
-        <v>113.6115886154763</v>
+        <v>113.483971351642</v>
       </c>
       <c r="O20" t="n">
-        <v>10.65887370295175</v>
+        <v>10.65288558802929</v>
       </c>
       <c r="P20" t="n">
-        <v>347.8250394348109</v>
+        <v>347.7733931490769</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32579,28 +32667,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1941006232014608</v>
+        <v>0.1960302805076024</v>
       </c>
       <c r="J21" t="n">
+        <v>345</v>
+      </c>
+      <c r="K21" t="n">
         <v>344</v>
       </c>
-      <c r="K21" t="n">
-        <v>343</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01837003905670276</v>
+        <v>0.01883224289979213</v>
       </c>
       <c r="M21" t="n">
-        <v>7.610539886089006</v>
+        <v>7.599452573768493</v>
       </c>
       <c r="N21" t="n">
-        <v>109.6098197212808</v>
+        <v>109.3258273888145</v>
       </c>
       <c r="O21" t="n">
-        <v>10.46947084246768</v>
+        <v>10.45589916692077</v>
       </c>
       <c r="P21" t="n">
-        <v>334.5519221398345</v>
+        <v>334.5305690247598</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32657,28 +32745,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4796034610666342</v>
+        <v>-0.4733516585458001</v>
       </c>
       <c r="J22" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K22" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1337653751027318</v>
+        <v>0.1309081990074917</v>
       </c>
       <c r="M22" t="n">
-        <v>7.105146110932597</v>
+        <v>7.111859798767202</v>
       </c>
       <c r="N22" t="n">
-        <v>80.99654275449869</v>
+        <v>81.12382301422427</v>
       </c>
       <c r="O22" t="n">
-        <v>8.999807928755963</v>
+        <v>9.006876429385732</v>
       </c>
       <c r="P22" t="n">
-        <v>356.6342983186487</v>
+        <v>356.5649952467835</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32735,28 +32823,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3071596076822212</v>
+        <v>-0.304206253210394</v>
       </c>
       <c r="J23" t="n">
+        <v>345</v>
+      </c>
+      <c r="K23" t="n">
         <v>344</v>
       </c>
-      <c r="K23" t="n">
-        <v>343</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06641039639262858</v>
+        <v>0.06551108488782476</v>
       </c>
       <c r="M23" t="n">
-        <v>6.531233942494501</v>
+        <v>6.525206206119481</v>
       </c>
       <c r="N23" t="n">
-        <v>72.21144257019853</v>
+        <v>72.08267016200828</v>
       </c>
       <c r="O23" t="n">
-        <v>8.497731613212936</v>
+        <v>8.490151362726596</v>
       </c>
       <c r="P23" t="n">
-        <v>350.6489232609003</v>
+        <v>350.6162421637476</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32794,7 +32882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X345"/>
+  <dimension ref="A1:X346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74687,6 +74775,128 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-37.75700664269824,174.82994428837617</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-37.75629921059863,174.82983526162747</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-37.755619861088384,174.8295554302354</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-37.75490957181685,174.82944073935664</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-37.75420973531281,174.82924634731512</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-37.75349469656409,174.82912771816248</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-37.75279546405793,174.82895025472317</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-37.752114506762574,174.828690351156</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-37.75143239156613,174.828437440726</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-37.750753630268605,174.82817027868228</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-37.750073201113096,174.8278968898037</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-37.74941422440808,174.82754312888866</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-37.74874966585382,174.8272234128179</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-37.74807824256361,174.82692882015124</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-37.74740223868549,174.82664974289665</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-37.74671876955864,174.82639916109758</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>-37.746052226725304,174.8260882153994</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>-37.74538994872224,174.82578648552092</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>-37.74470578541535,174.8255912156502</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>-37.74399568620663,174.82551736708555</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>-37.74331352252677,174.8252362289549</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>-37.74260200953258,174.82515453527867</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X346"/>
+  <dimension ref="A1:X348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27304,7 +27304,7 @@
         <v>340.33</v>
       </c>
       <c r="F346" t="n">
-        <v>338.61</v>
+        <v>334.46</v>
       </c>
       <c r="G346" t="n">
         <v>327.55</v>
@@ -27358,6 +27358,162 @@
         <v>347.74</v>
       </c>
       <c r="X346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="C347" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="D347" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="E347" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="F347" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="G347" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="H347" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="I347" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="J347" t="n">
+        <v>322.04</v>
+      </c>
+      <c r="K347" t="n">
+        <v>325.33</v>
+      </c>
+      <c r="L347" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="M347" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="N347" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="O347" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="P347" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>341.23</v>
+      </c>
+      <c r="R347" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="S347" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="T347" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="U347" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="V347" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="W347" t="n">
+        <v>346.57</v>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="C348" t="n">
+        <v>333.32</v>
+      </c>
+      <c r="D348" t="n">
+        <v>341.71</v>
+      </c>
+      <c r="E348" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="F348" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="G348" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="H348" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="I348" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="J348" t="n">
+        <v>318.53</v>
+      </c>
+      <c r="K348" t="n">
+        <v>322.72</v>
+      </c>
+      <c r="L348" t="n">
+        <v>326.57</v>
+      </c>
+      <c r="M348" t="n">
+        <v>326.94</v>
+      </c>
+      <c r="N348" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="O348" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="P348" t="n">
+        <v>340.23</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="R348" t="n">
+        <v>340.99</v>
+      </c>
+      <c r="S348" t="n">
+        <v>345.04</v>
+      </c>
+      <c r="T348" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="U348" t="n">
+        <v>344.72</v>
+      </c>
+      <c r="V348" t="n">
+        <v>355.13</v>
+      </c>
+      <c r="W348" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="X348" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27374,7 +27530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31017,6 +31173,26 @@
       </c>
       <c r="B364" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>
@@ -31185,28 +31361,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4005877371533592</v>
+        <v>-0.3875468345956142</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0904538007750002</v>
+        <v>0.08535233573879852</v>
       </c>
       <c r="M2" t="n">
-        <v>7.246005274189969</v>
+        <v>7.273203913209429</v>
       </c>
       <c r="N2" t="n">
-        <v>87.976999737553</v>
+        <v>88.26312158670802</v>
       </c>
       <c r="O2" t="n">
-        <v>9.379605521425354</v>
+        <v>9.394845479661068</v>
       </c>
       <c r="P2" t="n">
-        <v>339.920454009685</v>
+        <v>339.7752991195832</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31263,28 +31439,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3318940543357164</v>
+        <v>-0.3176235417056102</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02869507393565984</v>
+        <v>0.02652264448446306</v>
       </c>
       <c r="M3" t="n">
-        <v>10.48107881562698</v>
+        <v>10.50608435937551</v>
       </c>
       <c r="N3" t="n">
-        <v>203.602176870495</v>
+        <v>203.3809793005499</v>
       </c>
       <c r="O3" t="n">
-        <v>14.2689234657172</v>
+        <v>14.2611703341819</v>
       </c>
       <c r="P3" t="n">
-        <v>329.6348253618476</v>
+        <v>329.4764503214928</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31341,28 +31517,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2055904156867176</v>
+        <v>-0.1934428967537558</v>
       </c>
       <c r="J4" t="n">
+        <v>347</v>
+      </c>
+      <c r="K4" t="n">
         <v>345</v>
       </c>
-      <c r="K4" t="n">
-        <v>343</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.007712572063984235</v>
+        <v>0.006897420775366481</v>
       </c>
       <c r="M4" t="n">
-        <v>12.38258353723996</v>
+        <v>12.35567757862625</v>
       </c>
       <c r="N4" t="n">
-        <v>296.5690193201898</v>
+        <v>295.5455542013773</v>
       </c>
       <c r="O4" t="n">
-        <v>17.22117938238232</v>
+        <v>17.19143839826608</v>
       </c>
       <c r="P4" t="n">
-        <v>337.0510382110789</v>
+        <v>336.9159918896204</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31419,28 +31595,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5636993023605315</v>
+        <v>-0.5495319982400999</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06673525613616615</v>
+        <v>0.06409576680885332</v>
       </c>
       <c r="M5" t="n">
-        <v>11.90705942979066</v>
+        <v>11.90092681783722</v>
       </c>
       <c r="N5" t="n">
-        <v>243.8916268694085</v>
+        <v>243.4358191563257</v>
       </c>
       <c r="O5" t="n">
-        <v>15.61703002716613</v>
+        <v>15.60242991191839</v>
       </c>
       <c r="P5" t="n">
-        <v>338.0235893450347</v>
+        <v>337.866862504297</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31497,28 +31673,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7584685855113038</v>
+        <v>-0.7403472143536408</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09429109304075489</v>
+        <v>0.09083289788815119</v>
       </c>
       <c r="M6" t="n">
-        <v>13.32742955670615</v>
+        <v>13.32593375284554</v>
       </c>
       <c r="N6" t="n">
-        <v>299.6547957987735</v>
+        <v>299.2531203780425</v>
       </c>
       <c r="O6" t="n">
-        <v>17.3105400204261</v>
+        <v>17.29893408213473</v>
       </c>
       <c r="P6" t="n">
-        <v>331.5148293677081</v>
+        <v>331.3124505385284</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31575,28 +31751,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08183838844092822</v>
+        <v>0.09269478226983924</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00189479295343864</v>
+        <v>0.002450672597229864</v>
       </c>
       <c r="M7" t="n">
-        <v>11.07498361064214</v>
+        <v>11.06059954632883</v>
       </c>
       <c r="N7" t="n">
-        <v>195.2917924159455</v>
+        <v>194.7329097842083</v>
       </c>
       <c r="O7" t="n">
-        <v>13.97468398268617</v>
+        <v>13.95467340299329</v>
       </c>
       <c r="P7" t="n">
-        <v>312.1514999679822</v>
+        <v>312.0320976009637</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31653,28 +31829,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4027656629349165</v>
+        <v>-0.3961956258169866</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0305928983148922</v>
+        <v>0.02994463061102348</v>
       </c>
       <c r="M8" t="n">
-        <v>12.95450887960407</v>
+        <v>12.90767541921119</v>
       </c>
       <c r="N8" t="n">
-        <v>284.6329165079598</v>
+        <v>283.2105515293721</v>
       </c>
       <c r="O8" t="n">
-        <v>16.87106743830869</v>
+        <v>16.82886067235011</v>
       </c>
       <c r="P8" t="n">
-        <v>321.5615905122172</v>
+        <v>321.489336645929</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31731,28 +31907,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.291019090979146</v>
+        <v>-0.2865810616818825</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02812298253786383</v>
+        <v>0.02759002871663996</v>
       </c>
       <c r="M9" t="n">
-        <v>9.665465980846319</v>
+        <v>9.625619179778813</v>
       </c>
       <c r="N9" t="n">
-        <v>159.8188950717118</v>
+        <v>158.9893968527009</v>
       </c>
       <c r="O9" t="n">
-        <v>12.64194981289325</v>
+        <v>12.60909976376985</v>
       </c>
       <c r="P9" t="n">
-        <v>326.7763660424712</v>
+        <v>326.7271180734218</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31809,28 +31985,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4029151593925033</v>
+        <v>-0.3932285263849765</v>
       </c>
       <c r="J10" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K10" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03671914610674443</v>
+        <v>0.03536233789954679</v>
       </c>
       <c r="M10" t="n">
-        <v>13.00092737511338</v>
+        <v>12.9682974994108</v>
       </c>
       <c r="N10" t="n">
-        <v>233.3665941388373</v>
+        <v>232.4633905930242</v>
       </c>
       <c r="O10" t="n">
-        <v>15.27634099314483</v>
+        <v>15.24675016497038</v>
       </c>
       <c r="P10" t="n">
-        <v>322.2988324967897</v>
+        <v>322.1912098419871</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31887,28 +32063,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2576522818173838</v>
+        <v>-0.2484507821237765</v>
       </c>
       <c r="J11" t="n">
+        <v>347</v>
+      </c>
+      <c r="K11" t="n">
         <v>345</v>
       </c>
-      <c r="K11" t="n">
-        <v>343</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02081572263067688</v>
+        <v>0.01956010761510507</v>
       </c>
       <c r="M11" t="n">
-        <v>10.87470759042915</v>
+        <v>10.84964805608988</v>
       </c>
       <c r="N11" t="n">
-        <v>170.4691028679715</v>
+        <v>169.8881371530368</v>
       </c>
       <c r="O11" t="n">
-        <v>13.05638169126391</v>
+        <v>13.03411436013344</v>
       </c>
       <c r="P11" t="n">
-        <v>322.580396233307</v>
+        <v>322.4781707942582</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31965,28 +32141,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4569126335511384</v>
+        <v>-0.4545265176388892</v>
       </c>
       <c r="J12" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K12" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1411794348637626</v>
+        <v>0.1412662033492514</v>
       </c>
       <c r="M12" t="n">
-        <v>6.843193658358786</v>
+        <v>6.814099562651851</v>
       </c>
       <c r="N12" t="n">
-        <v>69.34777927008257</v>
+        <v>68.97864669667824</v>
       </c>
       <c r="O12" t="n">
-        <v>8.327531403127974</v>
+        <v>8.305338445643153</v>
       </c>
       <c r="P12" t="n">
-        <v>337.5833112255758</v>
+        <v>337.556840442002</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32043,28 +32219,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5356040769204072</v>
+        <v>-0.5310252650418468</v>
       </c>
       <c r="J13" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K13" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05170219700009182</v>
+        <v>0.05141030595151053</v>
       </c>
       <c r="M13" t="n">
-        <v>13.51916098001008</v>
+        <v>13.45484774301514</v>
       </c>
       <c r="N13" t="n">
-        <v>289.4792721385528</v>
+        <v>287.9242235756419</v>
       </c>
       <c r="O13" t="n">
-        <v>17.01409039997592</v>
+        <v>16.96833001728932</v>
       </c>
       <c r="P13" t="n">
-        <v>340.0615946579476</v>
+        <v>340.0109419123213</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32121,28 +32297,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4263319639965599</v>
+        <v>-0.4179383332125946</v>
       </c>
       <c r="J14" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K14" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04407505425314218</v>
+        <v>0.04283925901575414</v>
       </c>
       <c r="M14" t="n">
-        <v>11.66435844504998</v>
+        <v>11.63174673801026</v>
       </c>
       <c r="N14" t="n">
-        <v>214.5153170850826</v>
+        <v>213.5953921569801</v>
       </c>
       <c r="O14" t="n">
-        <v>14.64634142320472</v>
+        <v>14.61490308407757</v>
       </c>
       <c r="P14" t="n">
-        <v>340.7454948784457</v>
+        <v>340.6517845903055</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32199,28 +32375,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3219803022045273</v>
+        <v>-0.3153518865229717</v>
       </c>
       <c r="J15" t="n">
+        <v>347</v>
+      </c>
+      <c r="K15" t="n">
         <v>345</v>
       </c>
-      <c r="K15" t="n">
-        <v>343</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05169335357342897</v>
+        <v>0.05014807052894099</v>
       </c>
       <c r="M15" t="n">
-        <v>7.292976164719271</v>
+        <v>7.276660710855322</v>
       </c>
       <c r="N15" t="n">
-        <v>103.8191441793165</v>
+        <v>103.4249053439376</v>
       </c>
       <c r="O15" t="n">
-        <v>10.18916798268222</v>
+        <v>10.16980360400031</v>
       </c>
       <c r="P15" t="n">
-        <v>344.4099979105121</v>
+        <v>344.3363531380884</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32277,28 +32453,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8331026219073825</v>
+        <v>-0.8197150155978842</v>
       </c>
       <c r="J16" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K16" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1710227911698439</v>
+        <v>0.1674472326305566</v>
       </c>
       <c r="M16" t="n">
-        <v>10.89967358252089</v>
+        <v>10.89108469217515</v>
       </c>
       <c r="N16" t="n">
-        <v>183.52231596398</v>
+        <v>183.3067234289933</v>
       </c>
       <c r="O16" t="n">
-        <v>13.54704085636343</v>
+        <v>13.53908133622785</v>
       </c>
       <c r="P16" t="n">
-        <v>351.7514496519253</v>
+        <v>351.6025007793497</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32355,28 +32531,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4987364342474288</v>
+        <v>-0.4901692701919023</v>
       </c>
       <c r="J17" t="n">
+        <v>347</v>
+      </c>
+      <c r="K17" t="n">
         <v>345</v>
       </c>
-      <c r="K17" t="n">
-        <v>343</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1152779242905158</v>
+        <v>0.1126184542595282</v>
       </c>
       <c r="M17" t="n">
-        <v>7.952947519369636</v>
+        <v>7.948864562464304</v>
       </c>
       <c r="N17" t="n">
-        <v>104.4640191367458</v>
+        <v>104.203762683774</v>
       </c>
       <c r="O17" t="n">
-        <v>10.22076411706805</v>
+        <v>10.20802442609607</v>
       </c>
       <c r="P17" t="n">
-        <v>346.7410202076528</v>
+        <v>346.645986491802</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32433,28 +32609,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5834739871942866</v>
+        <v>-0.5752297966794658</v>
       </c>
       <c r="J18" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K18" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1307388614308741</v>
+        <v>0.1285407730891774</v>
       </c>
       <c r="M18" t="n">
-        <v>8.795853186652755</v>
+        <v>8.776598901917714</v>
       </c>
       <c r="N18" t="n">
-        <v>123.6015146090878</v>
+        <v>123.2153598380476</v>
       </c>
       <c r="O18" t="n">
-        <v>11.11762180545317</v>
+        <v>11.10024143152065</v>
       </c>
       <c r="P18" t="n">
-        <v>350.4249163363968</v>
+        <v>350.3334346400562</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32511,28 +32687,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1925605397132484</v>
+        <v>-0.1843825824925376</v>
       </c>
       <c r="J19" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K19" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02081898980227059</v>
+        <v>0.01927729390409372</v>
       </c>
       <c r="M19" t="n">
-        <v>7.567971767319383</v>
+        <v>7.554715088312369</v>
       </c>
       <c r="N19" t="n">
-        <v>95.22986047881508</v>
+        <v>94.99831120977636</v>
       </c>
       <c r="O19" t="n">
-        <v>9.758578814500352</v>
+        <v>9.746707711313414</v>
       </c>
       <c r="P19" t="n">
-        <v>343.7198567381189</v>
+        <v>343.6291061395456</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32589,28 +32765,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2515474019427948</v>
+        <v>-0.2408648322165245</v>
       </c>
       <c r="J20" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K20" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02954709842407022</v>
+        <v>0.02734053801068703</v>
       </c>
       <c r="M20" t="n">
-        <v>8.644125832073817</v>
+        <v>8.644525720482493</v>
       </c>
       <c r="N20" t="n">
-        <v>113.483971351642</v>
+        <v>113.364345650474</v>
       </c>
       <c r="O20" t="n">
-        <v>10.65288558802929</v>
+        <v>10.64726939879301</v>
       </c>
       <c r="P20" t="n">
-        <v>347.7733931490769</v>
+        <v>347.6548278881899</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32667,28 +32843,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1960302805076024</v>
+        <v>0.2007533284258099</v>
       </c>
       <c r="J21" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K21" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01883224289979213</v>
+        <v>0.01993985778505958</v>
       </c>
       <c r="M21" t="n">
-        <v>7.599452573768493</v>
+        <v>7.582524901450521</v>
       </c>
       <c r="N21" t="n">
-        <v>109.3258273888145</v>
+        <v>108.8008068541095</v>
       </c>
       <c r="O21" t="n">
-        <v>10.45589916692077</v>
+        <v>10.43076252505585</v>
       </c>
       <c r="P21" t="n">
-        <v>334.5305690247598</v>
+        <v>334.4781430437069</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32745,28 +32921,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4733516585458001</v>
+        <v>-0.4610175223109269</v>
       </c>
       <c r="J22" t="n">
+        <v>347</v>
+      </c>
+      <c r="K22" t="n">
         <v>345</v>
       </c>
-      <c r="K22" t="n">
-        <v>343</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1309081990074917</v>
+        <v>0.1253275847605677</v>
       </c>
       <c r="M22" t="n">
-        <v>7.111859798767202</v>
+        <v>7.125640232606581</v>
       </c>
       <c r="N22" t="n">
-        <v>81.12382301422427</v>
+        <v>81.36639832746849</v>
       </c>
       <c r="O22" t="n">
-        <v>9.006876429385732</v>
+        <v>9.020332495394419</v>
       </c>
       <c r="P22" t="n">
-        <v>356.5649952467835</v>
+        <v>356.4278629099184</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32823,28 +32999,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.304206253210394</v>
+        <v>-0.2998861646704694</v>
       </c>
       <c r="J23" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K23" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06551108488782476</v>
+        <v>0.06440676843249127</v>
       </c>
       <c r="M23" t="n">
-        <v>6.525206206119481</v>
+        <v>6.506908280090168</v>
       </c>
       <c r="N23" t="n">
-        <v>72.08267016200828</v>
+        <v>71.75370952552915</v>
       </c>
       <c r="O23" t="n">
-        <v>8.490151362726596</v>
+        <v>8.470756136587166</v>
       </c>
       <c r="P23" t="n">
-        <v>350.6162421637476</v>
+        <v>350.5682983533833</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32882,7 +33058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X346"/>
+  <dimension ref="A1:X348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74803,7 +74979,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>-37.75420973531281,174.82924634731512</t>
+          <t>-37.7541999172789,174.82929179102524</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -74892,6 +75068,250 @@
         </is>
       </c>
       <c r="X346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-37.75700589340435,174.82994884470102</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-37.75629623170832,174.82985337562752</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-37.75561605985152,174.82957854483595</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-37.754904008828184,174.8294710347394</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-37.75419248868279,174.82932617493245</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-37.75348944907342,174.82915061492272</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-37.75278677614483,174.82898796418198</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-37.75211430355291,174.82869122218517</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-37.751426228906475,174.82846366502423</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-37.750750514123524,174.82818343687677</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-37.75007231214092,174.82790046330746</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-37.74940335654179,174.82758509601277</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-37.74873938476695,174.82726311404863</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-37.74807376496056,174.8269459588734</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-37.74739763814287,174.8266669495235</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-37.74671731346242,174.8264045302501</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>-37.746049110701534,174.82609970529364</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>-37.74539011447286,174.82578571914019</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>-37.744707262147216,174.82558140497883</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>-37.74399603279959,174.82551490921915</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>-37.7433134722622,174.82523656342212</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>-37.74259997015167,174.82516756013902</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-37.75700627718904,174.82994651097368</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-37.75629484277692,174.82986182141843</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-37.755612953068045,174.8295974365749</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-37.75489657796272,174.8295115022869</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-37.75418411375684,174.82936493894647</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-37.753483676828665,174.8291758013551</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-37.75277823887764,174.82902501971049</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-37.752111357012126,174.82870385210748</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-37.751417253404384,174.82850185891095</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-37.75074379251641,174.8282118194246</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-37.75006727462995,174.82792071316038</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-37.74938718043606,174.82764756119428</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-37.74873469122291,174.82728123851973</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-37.74807097701779,174.82695663015218</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-37.747390047242156,174.82669534045297</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-37.74671690575544,174.82640603361278</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-37.746041626415625,174.82612730251205</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-37.745385615525386,174.82580652090138</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-37.7447089234696,174.82557036797303</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>-37.74399806509359,174.82550049718392</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>-37.74331370683019,174.8252350025751</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>-37.74259932521896,174.82517167911178</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0221/nzd0221.xlsx
+++ b/data/nzd0221/nzd0221.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X348"/>
+  <dimension ref="A1:X350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27519,6 +27519,162 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>342.56</v>
+      </c>
+      <c r="C349" t="n">
+        <v>335.63</v>
+      </c>
+      <c r="D349" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="E349" t="n">
+        <v>332.87</v>
+      </c>
+      <c r="F349" t="n">
+        <v>319.62</v>
+      </c>
+      <c r="G349" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="H349" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="I349" t="n">
+        <v>314.95</v>
+      </c>
+      <c r="J349" t="n">
+        <v>309.85</v>
+      </c>
+      <c r="K349" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="L349" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="M349" t="n">
+        <v>317.02</v>
+      </c>
+      <c r="N349" t="n">
+        <v>333.87</v>
+      </c>
+      <c r="O349" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="P349" t="n">
+        <v>339.82</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="R349" t="n">
+        <v>341.39</v>
+      </c>
+      <c r="S349" t="n">
+        <v>347.79</v>
+      </c>
+      <c r="T349" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="U349" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="V349" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="W349" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>343.67</v>
+      </c>
+      <c r="C350" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="D350" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="E350" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="F350" t="n">
+        <v>310.61</v>
+      </c>
+      <c r="G350" t="n">
+        <v>311.5</v>
+      </c>
+      <c r="H350" t="n">
+        <v>299.96</v>
+      </c>
+      <c r="I350" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="J350" t="n">
+        <v>302.7</v>
+      </c>
+      <c r="K350" t="n">
+        <v>315.45</v>
+      </c>
+      <c r="L350" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="M350" t="n">
+        <v>309.4</v>
+      </c>
+      <c r="N350" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="O350" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="P350" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="R350" t="n">
+        <v>343.56</v>
+      </c>
+      <c r="S350" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="T350" t="n">
+        <v>359.05</v>
+      </c>
+      <c r="U350" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="V350" t="n">
+        <v>354.7</v>
+      </c>
+      <c r="W350" t="n">
+        <v>342.53</v>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27530,7 +27686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31193,6 +31349,26 @@
       </c>
       <c r="B366" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -31361,28 +31537,28 @@
         <v>0.0998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3875468345956142</v>
+        <v>-0.3724507458310898</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08535233573879852</v>
+        <v>0.07930421061278747</v>
       </c>
       <c r="M2" t="n">
-        <v>7.273203913209429</v>
+        <v>7.311394633527544</v>
       </c>
       <c r="N2" t="n">
-        <v>88.26312158670802</v>
+        <v>88.83204854961096</v>
       </c>
       <c r="O2" t="n">
-        <v>9.394845479661068</v>
+        <v>9.425075519570703</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7752991195832</v>
+        <v>339.606435586281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31439,28 +31615,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3176235417056102</v>
+        <v>-0.3003295212141178</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02652264448446306</v>
+        <v>0.02388732544012873</v>
       </c>
       <c r="M3" t="n">
-        <v>10.50608435937551</v>
+        <v>10.54901445501293</v>
       </c>
       <c r="N3" t="n">
-        <v>203.3809793005499</v>
+        <v>203.6327811689443</v>
       </c>
       <c r="O3" t="n">
-        <v>14.2611703341819</v>
+        <v>14.26999583633241</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4764503214928</v>
+        <v>329.2835601874353</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31517,28 +31693,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1934428967537558</v>
+        <v>-0.1767837947722985</v>
       </c>
       <c r="J4" t="n">
+        <v>349</v>
+      </c>
+      <c r="K4" t="n">
         <v>347</v>
       </c>
-      <c r="K4" t="n">
-        <v>345</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.006897420775366481</v>
+        <v>0.005807968837482469</v>
       </c>
       <c r="M4" t="n">
-        <v>12.35567757862625</v>
+        <v>12.3453275035001</v>
       </c>
       <c r="N4" t="n">
-        <v>295.5455542013773</v>
+        <v>295.1717861989806</v>
       </c>
       <c r="O4" t="n">
-        <v>17.19143839826608</v>
+        <v>17.18056419908789</v>
       </c>
       <c r="P4" t="n">
-        <v>336.9159918896204</v>
+        <v>336.729843573512</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31595,28 +31771,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5495319982400999</v>
+        <v>-0.5439041756823355</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06409576680885332</v>
+        <v>0.06349482721552901</v>
       </c>
       <c r="M5" t="n">
-        <v>11.90092681783722</v>
+        <v>11.85693897613067</v>
       </c>
       <c r="N5" t="n">
-        <v>243.4358191563257</v>
+        <v>242.3032011827792</v>
       </c>
       <c r="O5" t="n">
-        <v>15.60242991191839</v>
+        <v>15.56609139067284</v>
       </c>
       <c r="P5" t="n">
-        <v>337.866862504297</v>
+        <v>337.804344319815</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31673,28 +31849,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7403472143536408</v>
+        <v>-0.7362382806023643</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09083289788815119</v>
+        <v>0.0908226513864977</v>
       </c>
       <c r="M6" t="n">
-        <v>13.32593375284554</v>
+        <v>13.27062838941272</v>
       </c>
       <c r="N6" t="n">
-        <v>299.2531203780425</v>
+        <v>297.7147147476939</v>
       </c>
       <c r="O6" t="n">
-        <v>17.29893408213473</v>
+        <v>17.25441145758655</v>
       </c>
       <c r="P6" t="n">
-        <v>331.3124505385284</v>
+        <v>331.2664045792709</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31751,28 +31927,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09269478226983924</v>
+        <v>0.09249443788749315</v>
       </c>
       <c r="J7" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002450672597229864</v>
+        <v>0.002467873951576771</v>
       </c>
       <c r="M7" t="n">
-        <v>11.06059954632883</v>
+        <v>11.01356686815306</v>
       </c>
       <c r="N7" t="n">
-        <v>194.7329097842083</v>
+        <v>193.6607034023894</v>
       </c>
       <c r="O7" t="n">
-        <v>13.95467340299329</v>
+        <v>13.9162029089256</v>
       </c>
       <c r="P7" t="n">
-        <v>312.0320976009637</v>
+        <v>312.0343462494433</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31829,28 +32005,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3961956258169866</v>
+        <v>-0.4036751901764403</v>
       </c>
       <c r="J8" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02994463061102348</v>
+        <v>0.03136169232750463</v>
       </c>
       <c r="M8" t="n">
-        <v>12.90767541921119</v>
+        <v>12.88009574176557</v>
       </c>
       <c r="N8" t="n">
-        <v>283.2105515293721</v>
+        <v>281.941515377822</v>
       </c>
       <c r="O8" t="n">
-        <v>16.82886067235011</v>
+        <v>16.79111417916697</v>
       </c>
       <c r="P8" t="n">
-        <v>321.489336645929</v>
+        <v>321.5720722231868</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31907,28 +32083,28 @@
         <v>0.0992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2865810616818825</v>
+        <v>-0.2947747335594352</v>
       </c>
       <c r="J9" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02759002871663996</v>
+        <v>0.02940489004482782</v>
       </c>
       <c r="M9" t="n">
-        <v>9.625619179778813</v>
+        <v>9.625979563441994</v>
       </c>
       <c r="N9" t="n">
-        <v>158.9893968527009</v>
+        <v>158.459495850894</v>
       </c>
       <c r="O9" t="n">
-        <v>12.60909976376985</v>
+        <v>12.58806958397093</v>
       </c>
       <c r="P9" t="n">
-        <v>326.7271180734218</v>
+        <v>326.8185413343499</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31985,28 +32161,28 @@
         <v>0.0922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3932285263849765</v>
+        <v>-0.3990788875111943</v>
       </c>
       <c r="J10" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03536233789954679</v>
+        <v>0.03675550629002078</v>
       </c>
       <c r="M10" t="n">
-        <v>12.9682974994108</v>
+        <v>12.92810524761817</v>
       </c>
       <c r="N10" t="n">
-        <v>232.4633905930242</v>
+        <v>231.3482817013055</v>
       </c>
       <c r="O10" t="n">
-        <v>15.24675016497038</v>
+        <v>15.21013746490496</v>
       </c>
       <c r="P10" t="n">
-        <v>322.1912098419871</v>
+        <v>322.2565897625083</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32063,28 +32239,28 @@
         <v>0.0751</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2484507821237765</v>
+        <v>-0.2465670600015097</v>
       </c>
       <c r="J11" t="n">
+        <v>349</v>
+      </c>
+      <c r="K11" t="n">
         <v>347</v>
       </c>
-      <c r="K11" t="n">
-        <v>345</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01956010761510507</v>
+        <v>0.01948624045450786</v>
       </c>
       <c r="M11" t="n">
-        <v>10.84964805608988</v>
+        <v>10.79687661689966</v>
       </c>
       <c r="N11" t="n">
-        <v>169.8881371530368</v>
+        <v>168.9502977088507</v>
       </c>
       <c r="O11" t="n">
-        <v>13.03411436013344</v>
+        <v>12.99808823284604</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4781707942582</v>
+        <v>322.4571619699262</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32141,28 +32317,28 @@
         <v>0.0779</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4545265176388892</v>
+        <v>-0.4536465100865738</v>
       </c>
       <c r="J12" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K12" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1412662033492514</v>
+        <v>0.1422011046647184</v>
       </c>
       <c r="M12" t="n">
-        <v>6.814099562651851</v>
+        <v>6.778726867118031</v>
       </c>
       <c r="N12" t="n">
-        <v>68.97864669667824</v>
+        <v>68.58622195317803</v>
       </c>
       <c r="O12" t="n">
-        <v>8.305338445643153</v>
+        <v>8.281679899222018</v>
       </c>
       <c r="P12" t="n">
-        <v>337.556840442002</v>
+        <v>337.5470288078669</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32219,28 +32395,28 @@
         <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5310252650418468</v>
+        <v>-0.5448121960415216</v>
       </c>
       <c r="J13" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05141030595151053</v>
+        <v>0.05439157244320336</v>
       </c>
       <c r="M13" t="n">
-        <v>13.45484774301514</v>
+        <v>13.47563048200417</v>
       </c>
       <c r="N13" t="n">
-        <v>287.9242235756419</v>
+        <v>287.2238556329445</v>
       </c>
       <c r="O13" t="n">
-        <v>16.96833001728932</v>
+        <v>16.94767994838658</v>
       </c>
       <c r="P13" t="n">
-        <v>340.0109419123213</v>
+        <v>340.164371586987</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32297,28 +32473,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4179383332125946</v>
+        <v>-0.4167604465999734</v>
       </c>
       <c r="J14" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K14" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04283925901575414</v>
+        <v>0.04306906419635537</v>
       </c>
       <c r="M14" t="n">
-        <v>11.63174673801026</v>
+        <v>11.58261101458082</v>
       </c>
       <c r="N14" t="n">
-        <v>213.5953921569801</v>
+        <v>212.4267112062449</v>
       </c>
       <c r="O14" t="n">
-        <v>14.61490308407757</v>
+        <v>14.57486573544487</v>
       </c>
       <c r="P14" t="n">
-        <v>340.6517845903055</v>
+        <v>340.6386089836107</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32375,28 +32551,28 @@
         <v>0.123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3153518865229717</v>
+        <v>-0.3111186591401204</v>
       </c>
       <c r="J15" t="n">
+        <v>349</v>
+      </c>
+      <c r="K15" t="n">
         <v>347</v>
       </c>
-      <c r="K15" t="n">
-        <v>345</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.05014807052894099</v>
+        <v>0.04937767110561186</v>
       </c>
       <c r="M15" t="n">
-        <v>7.276660710855322</v>
+        <v>7.25169531488243</v>
       </c>
       <c r="N15" t="n">
-        <v>103.4249053439376</v>
+        <v>102.9183317572479</v>
       </c>
       <c r="O15" t="n">
-        <v>10.16980360400031</v>
+        <v>10.14486726168696</v>
       </c>
       <c r="P15" t="n">
-        <v>344.3363531380884</v>
+        <v>344.2890957886622</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32453,28 +32629,28 @@
         <v>0.0663</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8197150155978842</v>
+        <v>-0.8083330210956842</v>
       </c>
       <c r="J16" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K16" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1674472326305566</v>
+        <v>0.1647151434173371</v>
       </c>
       <c r="M16" t="n">
-        <v>10.89108469217515</v>
+        <v>10.87395346345107</v>
       </c>
       <c r="N16" t="n">
-        <v>183.3067234289933</v>
+        <v>182.860161823295</v>
       </c>
       <c r="O16" t="n">
-        <v>13.53908133622785</v>
+        <v>13.52257970297439</v>
       </c>
       <c r="P16" t="n">
-        <v>351.6025007793497</v>
+        <v>351.475226908585</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32531,28 +32707,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4901692701919023</v>
+        <v>-0.4814123966978192</v>
       </c>
       <c r="J17" t="n">
+        <v>349</v>
+      </c>
+      <c r="K17" t="n">
         <v>347</v>
       </c>
-      <c r="K17" t="n">
-        <v>345</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1126184542595282</v>
+        <v>0.1098503291651493</v>
       </c>
       <c r="M17" t="n">
-        <v>7.948864562464304</v>
+        <v>7.946161765335493</v>
       </c>
       <c r="N17" t="n">
-        <v>104.203762683774</v>
+        <v>103.9718819486153</v>
       </c>
       <c r="O17" t="n">
-        <v>10.20802442609607</v>
+        <v>10.19666033310001</v>
       </c>
       <c r="P17" t="n">
-        <v>346.645986491802</v>
+        <v>346.5483800897306</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32609,28 +32785,28 @@
         <v>0.0421</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5752297966794658</v>
+        <v>-0.5668914149814359</v>
       </c>
       <c r="J18" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K18" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1285407730891774</v>
+        <v>0.1262819780777131</v>
       </c>
       <c r="M18" t="n">
-        <v>8.776598901917714</v>
+        <v>8.758765474625582</v>
       </c>
       <c r="N18" t="n">
-        <v>123.2153598380476</v>
+        <v>122.8425711028952</v>
       </c>
       <c r="O18" t="n">
-        <v>11.10024143152065</v>
+        <v>11.08343679112644</v>
       </c>
       <c r="P18" t="n">
-        <v>350.3334346400562</v>
+        <v>350.240425284576</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32687,28 +32863,28 @@
         <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1843825824925376</v>
+        <v>-0.1726990639130172</v>
       </c>
       <c r="J19" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K19" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01927729390409372</v>
+        <v>0.01702970612624344</v>
       </c>
       <c r="M19" t="n">
-        <v>7.554715088312369</v>
+        <v>7.555413377967573</v>
       </c>
       <c r="N19" t="n">
-        <v>94.99831120977636</v>
+        <v>95.11136762451819</v>
       </c>
       <c r="O19" t="n">
-        <v>9.746707711313414</v>
+        <v>9.752505710047966</v>
       </c>
       <c r="P19" t="n">
-        <v>343.6291061395456</v>
+        <v>343.4987834660723</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32765,28 +32941,28 @@
         <v>0.0462</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2408648322165245</v>
+        <v>-0.2233568976156939</v>
       </c>
       <c r="J20" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K20" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02734053801068703</v>
+        <v>0.02357023540349656</v>
       </c>
       <c r="M20" t="n">
-        <v>8.644525720482493</v>
+        <v>8.67763184891683</v>
       </c>
       <c r="N20" t="n">
-        <v>113.364345650474</v>
+        <v>114.1813166778008</v>
       </c>
       <c r="O20" t="n">
-        <v>10.64726939879301</v>
+        <v>10.68556580990454</v>
       </c>
       <c r="P20" t="n">
-        <v>347.6548278881899</v>
+        <v>347.4595430329209</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32843,28 +33019,28 @@
         <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2007533284258099</v>
+        <v>0.2098387866920982</v>
       </c>
       <c r="J21" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K21" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01993985778505958</v>
+        <v>0.02191439357281766</v>
       </c>
       <c r="M21" t="n">
-        <v>7.582524901450521</v>
+        <v>7.590972857790628</v>
       </c>
       <c r="N21" t="n">
-        <v>108.8008068541095</v>
+        <v>108.5770813767334</v>
       </c>
       <c r="O21" t="n">
-        <v>10.43076252505585</v>
+        <v>10.42003269556931</v>
       </c>
       <c r="P21" t="n">
-        <v>334.4781430437069</v>
+        <v>334.3767977461158</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32921,28 +33097,28 @@
         <v>0.0545</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4610175223109269</v>
+        <v>-0.4490142912183258</v>
       </c>
       <c r="J22" t="n">
+        <v>349</v>
+      </c>
+      <c r="K22" t="n">
         <v>347</v>
       </c>
-      <c r="K22" t="n">
-        <v>345</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1253275847605677</v>
+        <v>0.1199974668194594</v>
       </c>
       <c r="M22" t="n">
-        <v>7.125640232606581</v>
+        <v>7.138239709734159</v>
       </c>
       <c r="N22" t="n">
-        <v>81.36639832746849</v>
+        <v>81.57857429525833</v>
       </c>
       <c r="O22" t="n">
-        <v>9.020332495394419</v>
+        <v>9.032085821960415</v>
       </c>
       <c r="P22" t="n">
-        <v>356.4278629099184</v>
+        <v>356.293758268221</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32999,28 +33175,28 @@
         <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2998861646704694</v>
+        <v>-0.2987404443803459</v>
       </c>
       <c r="J23" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K23" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06440676843249127</v>
+        <v>0.06463582386107491</v>
       </c>
       <c r="M23" t="n">
-        <v>6.506908280090168</v>
+        <v>6.474678490935355</v>
       </c>
       <c r="N23" t="n">
-        <v>71.75370952552915</v>
+        <v>71.35340605149527</v>
       </c>
       <c r="O23" t="n">
-        <v>8.470756136587166</v>
+        <v>8.447094533121746</v>
       </c>
       <c r="P23" t="n">
-        <v>350.5682983533833</v>
+        <v>350.555532450568</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33058,7 +33234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X348"/>
+  <dimension ref="A1:X350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75317,6 +75493,250 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-37.757008945405246,174.82993028601132</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-37.75629906439548,174.8298361506582</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-37.755619148356814,174.8295597642232</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-37.75489442585159,174.82952322239467</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-37.75416480879501,174.82945429324874</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-37.75346883388926,174.82924056644794</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-37.75276015992108,174.82910349021188</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-37.75209235687232,174.8287852933052</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-37.75139505752362,174.82859630984848</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-37.75073570597636,174.82824596547118</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-37.75006676279709,174.82792277063191</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-37.7493594658582,174.8277545826482</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-37.7487285728489,174.8273048650588</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-37.7480690902277,174.82696385212824</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-37.74738886835167,174.8266997496498</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-37.74672069160528,174.82639207381592</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-37.74604279128545,174.8261230072255</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>-37.74539212715872,174.82577641308828</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>-37.74471577012077,174.8255248821253</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>-37.744001278950314,174.8254777060567</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>-37.74331392464329,174.82523355321715</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>-37.742596466596574,174.82518993617938</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-37.75701097397911,174.8299179505939</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-37.75630313980555,174.82981136892562</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-37.755625800512036,174.82951931366694</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-37.75487556437558,174.82962593915724</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-37.75414349282225,174.82955295523388</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-37.7534545906317,174.82930271474376</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-37.752740247899794,174.82918991670374</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-37.75207495696319,174.82885987511233</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-37.751376773994565,174.8286741121315</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-37.75072506984362,174.8282908772976</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-37.75006538892978,174.8279282933185</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-37.74933817697461,174.82783679060347</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-37.748709631004076,174.8273780102088</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-37.748063964915154,174.82698347003142</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-37.747389443420225,174.8266975988221</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-37.74671530404923,174.82641193968024</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-37.746049110701534,174.82609970529364</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>-37.7453995385722,174.82574214491603</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>-37.744722046202426,174.82548318675694</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>-37.74400578464406,174.82544575378645</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>-37.74331298637131,174.8252397966052</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>-37.742592928175945,174.8252125348646</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
